--- a/research/traditional_assets/database/data/nigeria/nigeria_software_system_application.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_software_system_application.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.2291301988433363</v>
+        <v>0.2284743082468063</v>
       </c>
       <c r="C2">
-        <v>6.987588298688129</v>
+        <v>6.938344016226616</v>
       </c>
       <c r="D2">
-        <v>5.847588298688129</v>
+        <v>5.868584016226617</v>
       </c>
       <c r="E2">
-        <v>-0.954</v>
+        <v>-0.88376</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.07024</v>
       </c>
       <c r="G2">
         <v>1.14</v>
@@ -1445,28 +1445,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.003533072</v>
       </c>
       <c r="N2">
-        <v>0.7320408163265306</v>
+        <v>0.7285077443265306</v>
       </c>
       <c r="O2">
-        <v>0.2196122448979592</v>
+        <v>0.2185523232979592</v>
       </c>
       <c r="P2">
-        <v>0.5124285714285715</v>
+        <v>0.5099554210285715</v>
       </c>
       <c r="Q2">
-        <v>0.6324285714285715</v>
+        <v>0.6299554210285715</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.2291301988433363</v>
+        <v>0.230426472976572</v>
       </c>
       <c r="T2">
-        <v>1.278259280003682</v>
+        <v>1.287297476933001</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>207.1966878474401</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.2284743082468063</v>
+        <v>0.2278184176502763</v>
       </c>
       <c r="C3">
-        <v>6.938344016226616</v>
+        <v>6.88925104695504</v>
       </c>
       <c r="D3">
-        <v>5.868584016226617</v>
+        <v>5.88973104695504</v>
       </c>
       <c r="E3">
-        <v>-0.88376</v>
+        <v>-0.81352</v>
       </c>
       <c r="F3">
-        <v>0.07024</v>
+        <v>0.14048</v>
       </c>
       <c r="G3">
         <v>1.14</v>
@@ -1527,28 +1527,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M3">
-        <v>0.003533072</v>
+        <v>0.007066143999999999</v>
       </c>
       <c r="N3">
-        <v>0.7285077443265306</v>
+        <v>0.7249746723265306</v>
       </c>
       <c r="O3">
-        <v>0.2185523232979592</v>
+        <v>0.2174924016979592</v>
       </c>
       <c r="P3">
-        <v>0.5099554210285715</v>
+        <v>0.5074822706285714</v>
       </c>
       <c r="Q3">
-        <v>0.6299554210285715</v>
+        <v>0.6274822706285714</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.230426472976572</v>
+        <v>0.2317492016839554</v>
       </c>
       <c r="T3">
-        <v>1.287297476933001</v>
+        <v>1.296520126860877</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>207.1966878474401</v>
+        <v>103.59834392372</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.2278184176502763</v>
+        <v>0.2271625270537463</v>
       </c>
       <c r="C4">
-        <v>6.88925104695504</v>
+        <v>6.840311032528374</v>
       </c>
       <c r="D4">
-        <v>5.88973104695504</v>
+        <v>5.911031032528375</v>
       </c>
       <c r="E4">
-        <v>-0.81352</v>
+        <v>-0.7432799999999999</v>
       </c>
       <c r="F4">
-        <v>0.14048</v>
+        <v>0.21072</v>
       </c>
       <c r="G4">
         <v>1.14</v>
@@ -1609,28 +1609,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M4">
-        <v>0.007066143999999999</v>
+        <v>0.010599216</v>
       </c>
       <c r="N4">
-        <v>0.7249746723265306</v>
+        <v>0.7214416003265306</v>
       </c>
       <c r="O4">
-        <v>0.2174924016979592</v>
+        <v>0.2164324800979592</v>
       </c>
       <c r="P4">
-        <v>0.5074822706285714</v>
+        <v>0.5050091202285714</v>
       </c>
       <c r="Q4">
-        <v>0.6274822706285714</v>
+        <v>0.6250091202285714</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2317492016839554</v>
+        <v>0.233099203148192</v>
       </c>
       <c r="T4">
-        <v>1.296520126860877</v>
+        <v>1.305932934519225</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>103.59834392372</v>
+        <v>69.06556261581333</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.2271625270537463</v>
+        <v>0.2265066364572162</v>
       </c>
       <c r="C5">
-        <v>6.840311032528374</v>
+        <v>6.791525638435727</v>
       </c>
       <c r="D5">
-        <v>5.911031032528375</v>
+        <v>5.932485638435728</v>
       </c>
       <c r="E5">
-        <v>-0.7432799999999999</v>
+        <v>-0.67304</v>
       </c>
       <c r="F5">
-        <v>0.21072</v>
+        <v>0.28096</v>
       </c>
       <c r="G5">
         <v>1.14</v>
@@ -1691,28 +1691,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M5">
-        <v>0.010599216</v>
+        <v>0.014132288</v>
       </c>
       <c r="N5">
-        <v>0.7214416003265306</v>
+        <v>0.7179085283265306</v>
       </c>
       <c r="O5">
-        <v>0.2164324800979592</v>
+        <v>0.2153725584979592</v>
       </c>
       <c r="P5">
-        <v>0.5050091202285714</v>
+        <v>0.5025359698285714</v>
       </c>
       <c r="Q5">
-        <v>0.6250091202285714</v>
+        <v>0.6225359698285714</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.233099203148192</v>
+        <v>0.2344773296429336</v>
       </c>
       <c r="T5">
-        <v>1.305932934519225</v>
+        <v>1.315541842337122</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>69.06556261581333</v>
+        <v>51.79917196186001</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2265066364572162</v>
+        <v>0.2258507458606862</v>
       </c>
       <c r="C6">
-        <v>6.791525638435727</v>
+        <v>6.742896554434431</v>
       </c>
       <c r="D6">
-        <v>5.932485638435728</v>
+        <v>5.954096554434432</v>
       </c>
       <c r="E6">
-        <v>-0.67304</v>
+        <v>-0.6028</v>
       </c>
       <c r="F6">
-        <v>0.28096</v>
+        <v>0.3512</v>
       </c>
       <c r="G6">
         <v>1.14</v>
@@ -1773,28 +1773,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M6">
-        <v>0.014132288</v>
+        <v>0.01766536</v>
       </c>
       <c r="N6">
-        <v>0.7179085283265306</v>
+        <v>0.7143754563265307</v>
       </c>
       <c r="O6">
-        <v>0.2153725584979592</v>
+        <v>0.2143126368979592</v>
       </c>
       <c r="P6">
-        <v>0.5025359698285714</v>
+        <v>0.5000628194285714</v>
       </c>
       <c r="Q6">
-        <v>0.6225359698285714</v>
+        <v>0.6200628194285714</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2344773296429336</v>
+        <v>0.2358844693270382</v>
       </c>
       <c r="T6">
-        <v>1.315541842337122</v>
+        <v>1.325353042951186</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>51.79917196186001</v>
+        <v>41.43933756948801</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2258507458606862</v>
+        <v>0.2251948552641562</v>
       </c>
       <c r="C7">
-        <v>6.742896554434431</v>
+        <v>6.694425494993707</v>
       </c>
       <c r="D7">
-        <v>5.954096554434432</v>
+        <v>5.975865494993707</v>
       </c>
       <c r="E7">
-        <v>-0.6028</v>
+        <v>-0.5325599999999999</v>
       </c>
       <c r="F7">
-        <v>0.3512</v>
+        <v>0.42144</v>
       </c>
       <c r="G7">
         <v>1.14</v>
@@ -1855,28 +1855,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M7">
-        <v>0.01766536</v>
+        <v>0.021198432</v>
       </c>
       <c r="N7">
-        <v>0.7143754563265307</v>
+        <v>0.7108423843265306</v>
       </c>
       <c r="O7">
-        <v>0.2143126368979592</v>
+        <v>0.2132527152979592</v>
       </c>
       <c r="P7">
-        <v>0.5000628194285714</v>
+        <v>0.4975896690285714</v>
       </c>
       <c r="Q7">
-        <v>0.6200628194285714</v>
+        <v>0.6175896690285714</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.2358844693270382</v>
+        <v>0.2373215481533577</v>
       </c>
       <c r="T7">
-        <v>1.325353042951186</v>
+        <v>1.335372992514485</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>41.43933756948801</v>
+        <v>34.53278130790667</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.2251948552641562</v>
+        <v>0.2245389646676263</v>
       </c>
       <c r="C8">
-        <v>6.694425494993707</v>
+        <v>6.646114199748054</v>
       </c>
       <c r="D8">
-        <v>5.975865494993707</v>
+        <v>5.997794199748054</v>
       </c>
       <c r="E8">
-        <v>-0.5325599999999999</v>
+        <v>-0.46232</v>
       </c>
       <c r="F8">
-        <v>0.42144</v>
+        <v>0.49168</v>
       </c>
       <c r="G8">
         <v>1.14</v>
@@ -1937,28 +1937,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M8">
-        <v>0.021198432</v>
+        <v>0.024731504</v>
       </c>
       <c r="N8">
-        <v>0.7108423843265306</v>
+        <v>0.7073093123265306</v>
       </c>
       <c r="O8">
-        <v>0.2132527152979592</v>
+        <v>0.2121927936979592</v>
       </c>
       <c r="P8">
-        <v>0.4975896690285714</v>
+        <v>0.4951165186285714</v>
       </c>
       <c r="Q8">
-        <v>0.6175896690285714</v>
+        <v>0.6151165186285714</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2373215481533577</v>
+        <v>0.2387895319006734</v>
       </c>
       <c r="T8">
-        <v>1.335372992514485</v>
+        <v>1.345608424864091</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>34.53278130790667</v>
+        <v>29.59952683534858</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.2245389646676262</v>
+        <v>0.2238830740710963</v>
       </c>
       <c r="C9">
-        <v>6.646114199748056</v>
+        <v>6.597964433960692</v>
       </c>
       <c r="D9">
-        <v>5.997794199748056</v>
+        <v>6.019884433960693</v>
       </c>
       <c r="E9">
-        <v>-0.4623199999999999</v>
+        <v>-0.39208</v>
       </c>
       <c r="F9">
-        <v>0.4916800000000001</v>
+        <v>0.56192</v>
       </c>
       <c r="G9">
         <v>1.14</v>
@@ -2019,28 +2019,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M9">
-        <v>0.024731504</v>
+        <v>0.028264576</v>
       </c>
       <c r="N9">
-        <v>0.7073093123265306</v>
+        <v>0.7037762403265306</v>
       </c>
       <c r="O9">
-        <v>0.2121927936979592</v>
+        <v>0.2111328720979592</v>
       </c>
       <c r="P9">
-        <v>0.4951165186285714</v>
+        <v>0.4926433682285715</v>
       </c>
       <c r="Q9">
-        <v>0.6151165186285714</v>
+        <v>0.6126433682285715</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2387895319006734</v>
+        <v>0.2402894283381481</v>
       </c>
       <c r="T9">
-        <v>1.345608424864091</v>
+        <v>1.356066366612602</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>29.59952683534857</v>
+        <v>25.89958598093001</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.2238830740710963</v>
+        <v>0.2232271834745662</v>
       </c>
       <c r="C10">
-        <v>6.597964433960692</v>
+        <v>6.549977988997248</v>
       </c>
       <c r="D10">
-        <v>6.019884433960693</v>
+        <v>6.042137988997248</v>
       </c>
       <c r="E10">
-        <v>-0.39208</v>
+        <v>-0.32184</v>
       </c>
       <c r="F10">
-        <v>0.56192</v>
+        <v>0.6321599999999999</v>
       </c>
       <c r="G10">
         <v>1.14</v>
@@ -2101,28 +2101,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M10">
-        <v>0.028264576</v>
+        <v>0.031797648</v>
       </c>
       <c r="N10">
-        <v>0.7037762403265306</v>
+        <v>0.7002431683265307</v>
       </c>
       <c r="O10">
-        <v>0.2111328720979592</v>
+        <v>0.2100729504979592</v>
       </c>
       <c r="P10">
-        <v>0.4926433682285715</v>
+        <v>0.4901702178285715</v>
       </c>
       <c r="Q10">
-        <v>0.6126433682285715</v>
+        <v>0.6101702178285715</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2402894283381481</v>
+        <v>0.2418222895324904</v>
       </c>
       <c r="T10">
-        <v>1.356066366612602</v>
+        <v>1.366754153234706</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.89958598093001</v>
+        <v>23.02185420527112</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.2232271834745662</v>
+        <v>0.2225712928780362</v>
       </c>
       <c r="C11">
-        <v>6.549977988997248</v>
+        <v>6.502156682810018</v>
       </c>
       <c r="D11">
-        <v>6.042137988997248</v>
+        <v>6.064556682810018</v>
       </c>
       <c r="E11">
-        <v>-0.32184</v>
+        <v>-0.2516</v>
       </c>
       <c r="F11">
-        <v>0.6321599999999999</v>
+        <v>0.7023999999999999</v>
       </c>
       <c r="G11">
         <v>1.14</v>
@@ -2183,28 +2183,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M11">
-        <v>0.031797648</v>
+        <v>0.03533072</v>
       </c>
       <c r="N11">
-        <v>0.7002431683265307</v>
+        <v>0.6967100963265306</v>
       </c>
       <c r="O11">
-        <v>0.2100729504979592</v>
+        <v>0.2090130288979592</v>
       </c>
       <c r="P11">
-        <v>0.4901702178285715</v>
+        <v>0.4876970674285714</v>
       </c>
       <c r="Q11">
-        <v>0.6101702178285715</v>
+        <v>0.6076970674285714</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2418222895324904</v>
+        <v>0.2433892143089291</v>
       </c>
       <c r="T11">
-        <v>1.366754153234706</v>
+        <v>1.37767944622619</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>23.02185420527112</v>
+        <v>20.719668784744</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.2225712928780362</v>
+        <v>0.2219154022815062</v>
       </c>
       <c r="C12">
-        <v>6.502156682810018</v>
+        <v>6.454502360433035</v>
       </c>
       <c r="D12">
-        <v>6.064556682810018</v>
+        <v>6.087142360433035</v>
       </c>
       <c r="E12">
-        <v>-0.2515999999999999</v>
+        <v>-0.18136</v>
       </c>
       <c r="F12">
-        <v>0.7024</v>
+        <v>0.77264</v>
       </c>
       <c r="G12">
         <v>1.14</v>
@@ -2265,28 +2265,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M12">
-        <v>0.03533072</v>
+        <v>0.038863792</v>
       </c>
       <c r="N12">
-        <v>0.6967100963265306</v>
+        <v>0.6931770243265306</v>
       </c>
       <c r="O12">
-        <v>0.2090130288979592</v>
+        <v>0.2079531072979592</v>
       </c>
       <c r="P12">
-        <v>0.4876970674285714</v>
+        <v>0.4852239170285714</v>
       </c>
       <c r="Q12">
-        <v>0.6076970674285714</v>
+        <v>0.6052239170285714</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2433892143089291</v>
+        <v>0.2449913508780969</v>
       </c>
       <c r="T12">
-        <v>1.37767944622619</v>
+        <v>1.388850251419731</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.719668784744</v>
+        <v>18.83606253158545</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.2219154022815062</v>
+        <v>0.2212595116849762</v>
       </c>
       <c r="C13">
-        <v>6.454502360433035</v>
+        <v>6.407016894488252</v>
       </c>
       <c r="D13">
-        <v>6.087142360433035</v>
+        <v>6.109896894488252</v>
       </c>
       <c r="E13">
-        <v>-0.18136</v>
+        <v>-0.11112</v>
       </c>
       <c r="F13">
-        <v>0.77264</v>
+        <v>0.84288</v>
       </c>
       <c r="G13">
         <v>1.14</v>
@@ -2347,28 +2347,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M13">
-        <v>0.038863792</v>
+        <v>0.042396864</v>
       </c>
       <c r="N13">
-        <v>0.6931770243265306</v>
+        <v>0.6896439523265306</v>
       </c>
       <c r="O13">
-        <v>0.2079531072979592</v>
+        <v>0.2068931856979592</v>
       </c>
       <c r="P13">
-        <v>0.4852239170285714</v>
+        <v>0.4827507666285714</v>
       </c>
       <c r="Q13">
-        <v>0.6052239170285714</v>
+        <v>0.6027507666285714</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2449913508780969</v>
+        <v>0.2466298996420184</v>
       </c>
       <c r="T13">
-        <v>1.388850251419731</v>
+        <v>1.400274938549488</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.83606253158545</v>
+        <v>17.26639065395334</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.2212595116849762</v>
+        <v>0.2206036210884462</v>
       </c>
       <c r="C14">
-        <v>6.407016894488252</v>
+        <v>6.359702185703102</v>
       </c>
       <c r="D14">
-        <v>6.109896894488252</v>
+        <v>6.132822185703103</v>
       </c>
       <c r="E14">
-        <v>-0.11112</v>
+        <v>-0.04087999999999992</v>
       </c>
       <c r="F14">
-        <v>0.84288</v>
+        <v>0.91312</v>
       </c>
       <c r="G14">
         <v>1.14</v>
@@ -2429,28 +2429,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M14">
-        <v>0.042396864</v>
+        <v>0.045929936</v>
       </c>
       <c r="N14">
-        <v>0.6896439523265306</v>
+        <v>0.6861108803265307</v>
       </c>
       <c r="O14">
-        <v>0.2068931856979592</v>
+        <v>0.2058332640979592</v>
       </c>
       <c r="P14">
-        <v>0.4827507666285714</v>
+        <v>0.4802776162285715</v>
       </c>
       <c r="Q14">
-        <v>0.6027507666285714</v>
+        <v>0.6002776162285715</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2466298996420184</v>
+        <v>0.2483061161936163</v>
       </c>
       <c r="T14">
-        <v>1.400274938549488</v>
+        <v>1.411962262164986</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.26639065395334</v>
+        <v>15.93820675749539</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.2206036210884462</v>
+        <v>0.2199477304919162</v>
       </c>
       <c r="C15">
-        <v>6.359702185703102</v>
+        <v>6.312560163439767</v>
       </c>
       <c r="D15">
-        <v>6.132822185703103</v>
+        <v>6.155920163439768</v>
       </c>
       <c r="E15">
-        <v>-0.04087999999999992</v>
+        <v>0.02936000000000016</v>
       </c>
       <c r="F15">
-        <v>0.91312</v>
+        <v>0.9833600000000001</v>
       </c>
       <c r="G15">
         <v>1.14</v>
@@ -2511,28 +2511,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M15">
-        <v>0.045929936</v>
+        <v>0.049463008</v>
       </c>
       <c r="N15">
-        <v>0.6861108803265307</v>
+        <v>0.6825778083265306</v>
       </c>
       <c r="O15">
-        <v>0.2058332640979592</v>
+        <v>0.2047733424979592</v>
       </c>
       <c r="P15">
-        <v>0.4802776162285715</v>
+        <v>0.4778044658285714</v>
       </c>
       <c r="Q15">
-        <v>0.6002776162285715</v>
+        <v>0.5978044658285714</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2483061161936163</v>
+        <v>0.2500213145254839</v>
       </c>
       <c r="T15">
-        <v>1.411962262164986</v>
+        <v>1.423921384004101</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.93820675749539</v>
+        <v>14.79976341767429</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.2199477304919162</v>
+        <v>0.2192918398953861</v>
       </c>
       <c r="C16">
-        <v>6.312560163439767</v>
+        <v>6.265592786236462</v>
       </c>
       <c r="D16">
-        <v>6.155920163439768</v>
+        <v>6.179192786236462</v>
       </c>
       <c r="E16">
-        <v>0.02936000000000016</v>
+        <v>0.09960000000000013</v>
       </c>
       <c r="F16">
-        <v>0.9833600000000001</v>
+        <v>1.0536</v>
       </c>
       <c r="G16">
         <v>1.14</v>
@@ -2593,28 +2593,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M16">
-        <v>0.049463008</v>
+        <v>0.05299608</v>
       </c>
       <c r="N16">
-        <v>0.6825778083265306</v>
+        <v>0.6790447363265306</v>
       </c>
       <c r="O16">
-        <v>0.2047733424979592</v>
+        <v>0.2037134208979592</v>
       </c>
       <c r="P16">
-        <v>0.4778044658285714</v>
+        <v>0.4753313154285714</v>
       </c>
       <c r="Q16">
-        <v>0.5978044658285714</v>
+        <v>0.5953313154285714</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2500213145254839</v>
+        <v>0.2517768704651602</v>
       </c>
       <c r="T16">
-        <v>1.423921384004101</v>
+        <v>1.436161896945313</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.79976341767429</v>
+        <v>13.81311252316267</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.2192918398953861</v>
+        <v>0.2186359492988561</v>
       </c>
       <c r="C17">
-        <v>6.265592786236462</v>
+        <v>6.218802042361014</v>
       </c>
       <c r="D17">
-        <v>6.179192786236462</v>
+        <v>6.202642042361014</v>
       </c>
       <c r="E17">
-        <v>0.09959999999999991</v>
+        <v>0.16984</v>
       </c>
       <c r="F17">
-        <v>1.0536</v>
+        <v>1.12384</v>
       </c>
       <c r="G17">
         <v>1.14</v>
@@ -2675,28 +2675,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M17">
-        <v>0.05299607999999999</v>
+        <v>0.05652915199999999</v>
       </c>
       <c r="N17">
-        <v>0.6790447363265306</v>
+        <v>0.6755116643265306</v>
       </c>
       <c r="O17">
-        <v>0.2037134208979592</v>
+        <v>0.2026534992979592</v>
       </c>
       <c r="P17">
-        <v>0.4753313154285714</v>
+        <v>0.4728581650285715</v>
       </c>
       <c r="Q17">
-        <v>0.5953313154285714</v>
+        <v>0.5928581650285715</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2517768704651602</v>
+        <v>0.2535742253557811</v>
       </c>
       <c r="T17">
-        <v>1.436161896945313</v>
+        <v>1.448693850670839</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>13.81311252316267</v>
+        <v>12.949792990465</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.2186359492988561</v>
+        <v>0.2181585587023261</v>
       </c>
       <c r="C18">
-        <v>6.218802042361014</v>
+        <v>6.165741827379861</v>
       </c>
       <c r="D18">
-        <v>6.202642042361014</v>
+        <v>6.219821827379862</v>
       </c>
       <c r="E18">
-        <v>0.16984</v>
+        <v>0.2400800000000001</v>
       </c>
       <c r="F18">
-        <v>1.12384</v>
+        <v>1.19408</v>
       </c>
       <c r="G18">
         <v>1.14</v>
@@ -2757,45 +2757,45 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M18">
-        <v>0.05652915199999999</v>
+        <v>0.061853344</v>
       </c>
       <c r="N18">
-        <v>0.6755116643265306</v>
+        <v>0.6701874723265306</v>
       </c>
       <c r="O18">
-        <v>0.2026534992979592</v>
+        <v>0.2010562416979592</v>
       </c>
       <c r="P18">
-        <v>0.4728581650285715</v>
+        <v>0.4691312306285714</v>
       </c>
       <c r="Q18">
-        <v>0.5928581650285715</v>
+        <v>0.5891312306285714</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2535742253557811</v>
+        <v>0.2554148900028026</v>
       </c>
       <c r="T18">
-        <v>1.448693850670839</v>
+        <v>1.461527779184933</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.3</v>
       </c>
       <c r="W18">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>12.949792990465</v>
+        <v>11.8351049270114</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.2181585587023261</v>
+        <v>0.2175131681057961</v>
       </c>
       <c r="C19">
-        <v>6.165741827379861</v>
+        <v>6.118879268747722</v>
       </c>
       <c r="D19">
-        <v>6.219821827379862</v>
+        <v>6.243199268747723</v>
       </c>
       <c r="E19">
-        <v>0.2400800000000001</v>
+        <v>0.3103200000000002</v>
       </c>
       <c r="F19">
-        <v>1.19408</v>
+        <v>1.26432</v>
       </c>
       <c r="G19">
         <v>1.14</v>
@@ -2839,28 +2839,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M19">
-        <v>0.061853344</v>
+        <v>0.065491776</v>
       </c>
       <c r="N19">
-        <v>0.6701874723265306</v>
+        <v>0.6665490403265306</v>
       </c>
       <c r="O19">
-        <v>0.2010562416979592</v>
+        <v>0.1999647120979592</v>
       </c>
       <c r="P19">
-        <v>0.4691312306285714</v>
+        <v>0.4665843282285714</v>
       </c>
       <c r="Q19">
-        <v>0.5891312306285714</v>
+        <v>0.5865843282285714</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2554148900028026</v>
+        <v>0.2573004489095075</v>
       </c>
       <c r="T19">
-        <v>1.461527779184933</v>
+        <v>1.474674730345711</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.8351049270114</v>
+        <v>11.17759909773298</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.2175131681057962</v>
+        <v>0.2168677775092661</v>
       </c>
       <c r="C20">
-        <v>6.118879268747722</v>
+        <v>6.072193103134183</v>
       </c>
       <c r="D20">
-        <v>6.243199268747722</v>
+        <v>6.266753103134183</v>
       </c>
       <c r="E20">
-        <v>0.3103199999999999</v>
+        <v>0.38056</v>
       </c>
       <c r="F20">
-        <v>1.26432</v>
+        <v>1.33456</v>
       </c>
       <c r="G20">
         <v>1.14</v>
@@ -2921,28 +2921,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M20">
-        <v>0.06549177599999999</v>
+        <v>0.069130208</v>
       </c>
       <c r="N20">
-        <v>0.6665490403265306</v>
+        <v>0.6629106083265306</v>
       </c>
       <c r="O20">
-        <v>0.1999647120979592</v>
+        <v>0.1988731824979592</v>
       </c>
       <c r="P20">
-        <v>0.4665843282285714</v>
+        <v>0.4640374258285714</v>
       </c>
       <c r="Q20">
-        <v>0.5865843282285714</v>
+        <v>0.5840374258285714</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2573004489095075</v>
+        <v>0.2592325648262545</v>
       </c>
       <c r="T20">
-        <v>1.474674730345711</v>
+        <v>1.488146297584533</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.17759909773299</v>
+        <v>10.58930440837861</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.2168677775092661</v>
+        <v>0.2162223869127362</v>
       </c>
       <c r="C21">
-        <v>6.072193103134183</v>
+        <v>6.025685334543479</v>
       </c>
       <c r="D21">
-        <v>6.266753103134183</v>
+        <v>6.290485334543479</v>
       </c>
       <c r="E21">
-        <v>0.38056</v>
+        <v>0.4508000000000001</v>
       </c>
       <c r="F21">
-        <v>1.33456</v>
+        <v>1.4048</v>
       </c>
       <c r="G21">
         <v>1.14</v>
@@ -3003,28 +3003,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M21">
-        <v>0.069130208</v>
+        <v>0.07276864</v>
       </c>
       <c r="N21">
-        <v>0.6629106083265306</v>
+        <v>0.6592721763265306</v>
       </c>
       <c r="O21">
-        <v>0.1988731824979592</v>
+        <v>0.1977816528979592</v>
       </c>
       <c r="P21">
-        <v>0.4640374258285714</v>
+        <v>0.4614905234285714</v>
       </c>
       <c r="Q21">
-        <v>0.5840374258285714</v>
+        <v>0.5814905234285714</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2592325648262545</v>
+        <v>0.2612129836409202</v>
       </c>
       <c r="T21">
-        <v>1.488146297584533</v>
+        <v>1.501954654004326</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.58930440837861</v>
+        <v>10.05983918795968</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.2162223869127362</v>
+        <v>0.2158268963162061</v>
       </c>
       <c r="C22">
-        <v>6.025685334543479</v>
+        <v>5.970077300728377</v>
       </c>
       <c r="D22">
-        <v>6.290485334543479</v>
+        <v>6.305117300728377</v>
       </c>
       <c r="E22">
-        <v>0.4508000000000001</v>
+        <v>0.5210400000000002</v>
       </c>
       <c r="F22">
-        <v>1.4048</v>
+        <v>1.47504</v>
       </c>
       <c r="G22">
         <v>1.14</v>
@@ -3085,45 +3085,45 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M22">
-        <v>0.07276864</v>
+        <v>0.07891464000000001</v>
       </c>
       <c r="N22">
-        <v>0.6592721763265306</v>
+        <v>0.6531261763265306</v>
       </c>
       <c r="O22">
-        <v>0.1977816528979592</v>
+        <v>0.1959378528979592</v>
       </c>
       <c r="P22">
-        <v>0.4614905234285714</v>
+        <v>0.4571883234285714</v>
       </c>
       <c r="Q22">
-        <v>0.5814905234285714</v>
+        <v>0.5771883234285714</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2612129836409202</v>
+        <v>0.2632435396407672</v>
       </c>
       <c r="T22">
-        <v>1.501954654004326</v>
+        <v>1.516112589067658</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.3</v>
       </c>
       <c r="W22">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>10.05983918795968</v>
+        <v>9.276362615688679</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2158268963162061</v>
+        <v>0.2151934057196761</v>
       </c>
       <c r="C23">
-        <v>5.97007730072838</v>
+        <v>5.923416922987347</v>
       </c>
       <c r="D23">
-        <v>6.30511730072838</v>
+        <v>6.328696922987347</v>
       </c>
       <c r="E23">
-        <v>0.5210399999999999</v>
+        <v>0.59128</v>
       </c>
       <c r="F23">
-        <v>1.47504</v>
+        <v>1.54528</v>
       </c>
       <c r="G23">
         <v>1.14</v>
@@ -3167,28 +3167,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M23">
-        <v>0.07891463999999999</v>
+        <v>0.08267247999999999</v>
       </c>
       <c r="N23">
-        <v>0.6531261763265306</v>
+        <v>0.6493683363265306</v>
       </c>
       <c r="O23">
-        <v>0.1959378528979592</v>
+        <v>0.1948105008979592</v>
       </c>
       <c r="P23">
-        <v>0.4571883234285714</v>
+        <v>0.4545578354285714</v>
       </c>
       <c r="Q23">
-        <v>0.5771883234285714</v>
+        <v>0.5745578354285714</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2632435396407672</v>
+        <v>0.2653261611790719</v>
       </c>
       <c r="T23">
-        <v>1.516112589067658</v>
+        <v>1.530633548106973</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.276362615688681</v>
+        <v>8.854709769521014</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.2151934057196761</v>
+        <v>0.2145599151231461</v>
       </c>
       <c r="C24">
-        <v>5.923416922987347</v>
+        <v>5.876933571514192</v>
       </c>
       <c r="D24">
-        <v>6.328696922987347</v>
+        <v>6.352453571514192</v>
       </c>
       <c r="E24">
-        <v>0.59128</v>
+        <v>0.6615200000000001</v>
       </c>
       <c r="F24">
-        <v>1.54528</v>
+        <v>1.61552</v>
       </c>
       <c r="G24">
         <v>1.14</v>
@@ -3249,28 +3249,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M24">
-        <v>0.08267247999999999</v>
+        <v>0.08643032</v>
       </c>
       <c r="N24">
-        <v>0.6493683363265306</v>
+        <v>0.6456104963265306</v>
       </c>
       <c r="O24">
-        <v>0.1948105008979592</v>
+        <v>0.1936831488979592</v>
       </c>
       <c r="P24">
-        <v>0.4545578354285714</v>
+        <v>0.4519273474285714</v>
       </c>
       <c r="Q24">
-        <v>0.5745578354285714</v>
+        <v>0.5719273474285714</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2653261611790719</v>
+        <v>0.2674628767833066</v>
       </c>
       <c r="T24">
-        <v>1.530633548106973</v>
+        <v>1.545531674913542</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.854709769521014</v>
+        <v>8.469722388237489</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2145599151231461</v>
+        <v>0.2139264245266161</v>
       </c>
       <c r="C25">
-        <v>5.876933571514192</v>
+        <v>5.830629247382982</v>
       </c>
       <c r="D25">
-        <v>6.352453571514192</v>
+        <v>6.376389247382982</v>
       </c>
       <c r="E25">
-        <v>0.6615200000000001</v>
+        <v>0.7317600000000002</v>
       </c>
       <c r="F25">
-        <v>1.61552</v>
+        <v>1.68576</v>
       </c>
       <c r="G25">
         <v>1.14</v>
@@ -3331,28 +3331,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M25">
-        <v>0.08643032</v>
+        <v>0.09018816</v>
       </c>
       <c r="N25">
-        <v>0.6456104963265306</v>
+        <v>0.6418526563265307</v>
       </c>
       <c r="O25">
-        <v>0.1936831488979592</v>
+        <v>0.1925557968979592</v>
       </c>
       <c r="P25">
-        <v>0.4519273474285714</v>
+        <v>0.4492968594285714</v>
       </c>
       <c r="Q25">
-        <v>0.5719273474285714</v>
+        <v>0.5692968594285714</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2674628767833066</v>
+        <v>0.2696558217455475</v>
       </c>
       <c r="T25">
-        <v>1.545531674913542</v>
+        <v>1.560821857688706</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.469722388237489</v>
+        <v>8.116817288727596</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.2139264245266161</v>
+        <v>0.2132929339300861</v>
       </c>
       <c r="C26">
-        <v>5.830629247382982</v>
+        <v>5.784505981941577</v>
       </c>
       <c r="D26">
-        <v>6.376389247382982</v>
+        <v>6.400505981941578</v>
       </c>
       <c r="E26">
-        <v>0.73176</v>
+        <v>0.802</v>
       </c>
       <c r="F26">
-        <v>1.68576</v>
+        <v>1.756</v>
       </c>
       <c r="G26">
         <v>1.14</v>
@@ -3413,28 +3413,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M26">
-        <v>0.09018815999999999</v>
+        <v>0.093946</v>
       </c>
       <c r="N26">
-        <v>0.6418526563265307</v>
+        <v>0.6380948163265306</v>
       </c>
       <c r="O26">
-        <v>0.1925557968979592</v>
+        <v>0.1914284448979592</v>
       </c>
       <c r="P26">
-        <v>0.4492968594285714</v>
+        <v>0.4466663714285715</v>
       </c>
       <c r="Q26">
-        <v>0.5692968594285714</v>
+        <v>0.5666663714285715</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2696558217455475</v>
+        <v>0.2719072452401148</v>
       </c>
       <c r="T26">
-        <v>1.560821857688706</v>
+        <v>1.576519778671208</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.116817288727598</v>
+        <v>7.792144597178492</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.2132929339300861</v>
+        <v>0.212805043333556</v>
       </c>
       <c r="C27">
-        <v>5.784505981941577</v>
+        <v>5.732964499179686</v>
       </c>
       <c r="D27">
-        <v>6.400505981941578</v>
+        <v>6.419204499179687</v>
       </c>
       <c r="E27">
-        <v>0.802</v>
+        <v>0.8722400000000001</v>
       </c>
       <c r="F27">
-        <v>1.756</v>
+        <v>1.82624</v>
       </c>
       <c r="G27">
         <v>1.14</v>
@@ -3495,45 +3495,45 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M27">
-        <v>0.093946</v>
+        <v>0.09916483200000001</v>
       </c>
       <c r="N27">
-        <v>0.6380948163265306</v>
+        <v>0.6328759843265306</v>
       </c>
       <c r="O27">
-        <v>0.1914284448979592</v>
+        <v>0.1898627952979592</v>
       </c>
       <c r="P27">
-        <v>0.4466663714285715</v>
+        <v>0.4430131890285715</v>
       </c>
       <c r="Q27">
-        <v>0.5666663714285715</v>
+        <v>0.5630131890285714</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2719072452401148</v>
+        <v>0.274219518018319</v>
       </c>
       <c r="T27">
-        <v>1.576519778671208</v>
+        <v>1.592641967788371</v>
       </c>
       <c r="U27">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.3</v>
       </c>
       <c r="W27">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.792144597178492</v>
+        <v>7.382060772578433</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.212805043333556</v>
+        <v>0.2121771527370261</v>
       </c>
       <c r="C28">
-        <v>5.732964499179686</v>
+        <v>5.686949929630514</v>
       </c>
       <c r="D28">
-        <v>6.419204499179687</v>
+        <v>6.443429929630515</v>
       </c>
       <c r="E28">
-        <v>0.8722400000000001</v>
+        <v>0.9424800000000002</v>
       </c>
       <c r="F28">
-        <v>1.82624</v>
+        <v>1.89648</v>
       </c>
       <c r="G28">
         <v>1.14</v>
@@ -3577,28 +3577,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M28">
-        <v>0.09916483200000001</v>
+        <v>0.102978864</v>
       </c>
       <c r="N28">
-        <v>0.6328759843265306</v>
+        <v>0.6290619523265306</v>
       </c>
       <c r="O28">
-        <v>0.1898627952979592</v>
+        <v>0.1887185856979592</v>
       </c>
       <c r="P28">
-        <v>0.4430131890285715</v>
+        <v>0.4403433666285714</v>
       </c>
       <c r="Q28">
-        <v>0.5630131890285714</v>
+        <v>0.5603433666285714</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.274219518018319</v>
+        <v>0.2765951407356522</v>
       </c>
       <c r="T28">
-        <v>1.592641967788371</v>
+        <v>1.609205860716964</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.382060772578433</v>
+        <v>7.108651114334787</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.2121771527370261</v>
+        <v>0.211549262140496</v>
       </c>
       <c r="C29">
-        <v>5.686949929630514</v>
+        <v>5.64111890141095</v>
       </c>
       <c r="D29">
-        <v>6.443429929630515</v>
+        <v>6.467838901410951</v>
       </c>
       <c r="E29">
-        <v>0.9424800000000002</v>
+        <v>1.01272</v>
       </c>
       <c r="F29">
-        <v>1.89648</v>
+        <v>1.96672</v>
       </c>
       <c r="G29">
         <v>1.14</v>
@@ -3659,28 +3659,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M29">
-        <v>0.102978864</v>
+        <v>0.106792896</v>
       </c>
       <c r="N29">
-        <v>0.6290619523265306</v>
+        <v>0.6252479203265306</v>
       </c>
       <c r="O29">
-        <v>0.1887185856979592</v>
+        <v>0.1875743760979592</v>
       </c>
       <c r="P29">
-        <v>0.4403433666285714</v>
+        <v>0.4376735442285715</v>
       </c>
       <c r="Q29">
-        <v>0.5603433666285714</v>
+        <v>0.5576735442285714</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2765951407356522</v>
+        <v>0.2790367529729111</v>
       </c>
       <c r="T29">
-        <v>1.609205860716964</v>
+        <v>1.626229861782462</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.108651114334787</v>
+        <v>6.85477071739426</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.211549262140496</v>
+        <v>0.210921371543966</v>
       </c>
       <c r="C30">
-        <v>5.64111890141095</v>
+        <v>5.595473508323995</v>
       </c>
       <c r="D30">
-        <v>6.467838901410951</v>
+        <v>6.492433508323995</v>
       </c>
       <c r="E30">
-        <v>1.01272</v>
+        <v>1.08296</v>
       </c>
       <c r="F30">
-        <v>1.96672</v>
+        <v>2.03696</v>
       </c>
       <c r="G30">
         <v>1.14</v>
@@ -3741,28 +3741,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M30">
-        <v>0.106792896</v>
+        <v>0.110606928</v>
       </c>
       <c r="N30">
-        <v>0.6252479203265306</v>
+        <v>0.6214338883265306</v>
       </c>
       <c r="O30">
-        <v>0.1875743760979592</v>
+        <v>0.1864301664979592</v>
       </c>
       <c r="P30">
-        <v>0.4376735442285715</v>
+        <v>0.4350037218285714</v>
       </c>
       <c r="Q30">
-        <v>0.5576735442285714</v>
+        <v>0.5550037218285714</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2790367529729111</v>
+        <v>0.2815471430196705</v>
       </c>
       <c r="T30">
-        <v>1.626229861782462</v>
+        <v>1.643733412173749</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.85477071739426</v>
+        <v>6.618399313346181</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.210921371543966</v>
+        <v>0.210293480947436</v>
       </c>
       <c r="C31">
-        <v>5.595473508323995</v>
+        <v>5.550015876141815</v>
       </c>
       <c r="D31">
-        <v>6.492433508323995</v>
+        <v>6.517215876141815</v>
       </c>
       <c r="E31">
-        <v>1.08296</v>
+        <v>1.1532</v>
       </c>
       <c r="F31">
-        <v>2.03696</v>
+        <v>2.1072</v>
       </c>
       <c r="G31">
         <v>1.14</v>
@@ -3823,28 +3823,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M31">
-        <v>0.110606928</v>
+        <v>0.11442096</v>
       </c>
       <c r="N31">
-        <v>0.6214338883265307</v>
+        <v>0.6176198563265306</v>
       </c>
       <c r="O31">
-        <v>0.1864301664979592</v>
+        <v>0.1852859568979592</v>
       </c>
       <c r="P31">
-        <v>0.4350037218285715</v>
+        <v>0.4323338994285714</v>
       </c>
       <c r="Q31">
-        <v>0.5550037218285715</v>
+        <v>0.5523338994285714</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2815471430196705</v>
+        <v>0.2841292584963372</v>
       </c>
       <c r="T31">
-        <v>1.643733412173749</v>
+        <v>1.661737064004786</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.618399313346184</v>
+        <v>6.39778600290131</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.210293480947436</v>
+        <v>0.209665590350906</v>
       </c>
       <c r="C32">
-        <v>5.550015876141815</v>
+        <v>5.50474816321821</v>
       </c>
       <c r="D32">
-        <v>6.517215876141815</v>
+        <v>6.54218816321821</v>
       </c>
       <c r="E32">
-        <v>1.1532</v>
+        <v>1.22344</v>
       </c>
       <c r="F32">
-        <v>2.1072</v>
+        <v>2.17744</v>
       </c>
       <c r="G32">
         <v>1.14</v>
@@ -3905,28 +3905,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M32">
-        <v>0.11442096</v>
+        <v>0.118234992</v>
       </c>
       <c r="N32">
-        <v>0.6176198563265306</v>
+        <v>0.6138058243265306</v>
       </c>
       <c r="O32">
-        <v>0.1852859568979592</v>
+        <v>0.1841417472979592</v>
       </c>
       <c r="P32">
-        <v>0.4323338994285714</v>
+        <v>0.4296640770285715</v>
       </c>
       <c r="Q32">
-        <v>0.5523338994285714</v>
+        <v>0.5496640770285715</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2841292584963372</v>
+        <v>0.2867862178998638</v>
       </c>
       <c r="T32">
-        <v>1.661737064004786</v>
+        <v>1.680262560816434</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.39778600290131</v>
+        <v>6.191405809259332</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.209665590350906</v>
+        <v>0.209261699754376</v>
       </c>
       <c r="C33">
-        <v>5.50474816321821</v>
+        <v>5.450672979097552</v>
       </c>
       <c r="D33">
-        <v>6.54218816321821</v>
+        <v>6.558352979097553</v>
       </c>
       <c r="E33">
-        <v>1.22344</v>
+        <v>1.29368</v>
       </c>
       <c r="F33">
-        <v>2.17744</v>
+        <v>2.24768</v>
       </c>
       <c r="G33">
         <v>1.14</v>
@@ -3987,45 +3987,45 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M33">
-        <v>0.118234992</v>
+        <v>0.124296704</v>
       </c>
       <c r="N33">
-        <v>0.6138058243265306</v>
+        <v>0.6077441123265306</v>
       </c>
       <c r="O33">
-        <v>0.1841417472979592</v>
+        <v>0.1823232336979592</v>
       </c>
       <c r="P33">
-        <v>0.4296640770285715</v>
+        <v>0.4254208786285714</v>
       </c>
       <c r="Q33">
-        <v>0.5496640770285715</v>
+        <v>0.5454208786285715</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2867862178998638</v>
+        <v>0.2895213231682</v>
       </c>
       <c r="T33">
-        <v>1.680262560816434</v>
+        <v>1.699332925181365</v>
       </c>
       <c r="U33">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V33">
         <v>0.3</v>
       </c>
       <c r="W33">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>6.191405809259332</v>
+        <v>5.889462815735891</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.209261699754376</v>
+        <v>0.208640809157846</v>
       </c>
       <c r="C34">
-        <v>5.450672979097552</v>
+        <v>5.405439116775847</v>
       </c>
       <c r="D34">
-        <v>6.558352979097553</v>
+        <v>6.583359116775847</v>
       </c>
       <c r="E34">
-        <v>1.29368</v>
+        <v>1.36392</v>
       </c>
       <c r="F34">
-        <v>2.24768</v>
+        <v>2.31792</v>
       </c>
       <c r="G34">
         <v>1.14</v>
@@ -4069,28 +4069,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M34">
-        <v>0.124296704</v>
+        <v>0.128180976</v>
       </c>
       <c r="N34">
-        <v>0.6077441123265306</v>
+        <v>0.6038598403265306</v>
       </c>
       <c r="O34">
-        <v>0.1823232336979592</v>
+        <v>0.1811579520979592</v>
       </c>
       <c r="P34">
-        <v>0.4254208786285714</v>
+        <v>0.4227018882285715</v>
       </c>
       <c r="Q34">
-        <v>0.5454208786285715</v>
+        <v>0.5427018882285715</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2895213231682</v>
+        <v>0.2923380733699195</v>
       </c>
       <c r="T34">
-        <v>1.699332925181365</v>
+        <v>1.718972554154205</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.889462815735891</v>
+        <v>5.710994245562076</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.208640809157846</v>
+        <v>0.208019918561316</v>
       </c>
       <c r="C35">
-        <v>5.405439116775847</v>
+        <v>5.360396674544571</v>
       </c>
       <c r="D35">
-        <v>6.583359116775847</v>
+        <v>6.608556674544571</v>
       </c>
       <c r="E35">
-        <v>1.36392</v>
+        <v>1.43416</v>
       </c>
       <c r="F35">
-        <v>2.31792</v>
+        <v>2.38816</v>
       </c>
       <c r="G35">
         <v>1.14</v>
@@ -4151,28 +4151,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M35">
-        <v>0.128180976</v>
+        <v>0.132065248</v>
       </c>
       <c r="N35">
-        <v>0.6038598403265306</v>
+        <v>0.5999755683265307</v>
       </c>
       <c r="O35">
-        <v>0.1811579520979592</v>
+        <v>0.1799926704979592</v>
       </c>
       <c r="P35">
-        <v>0.4227018882285715</v>
+        <v>0.4199828978285715</v>
       </c>
       <c r="Q35">
-        <v>0.5427018882285715</v>
+        <v>0.5399828978285715</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2923380733699195</v>
+        <v>0.2952401796383576</v>
       </c>
       <c r="T35">
-        <v>1.718972554154205</v>
+        <v>1.739207323398949</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.710994245562076</v>
+        <v>5.543023826574957</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.208019918561316</v>
+        <v>0.207399027964786</v>
       </c>
       <c r="C36">
-        <v>5.360396674544571</v>
+        <v>5.315547858808094</v>
       </c>
       <c r="D36">
-        <v>6.608556674544571</v>
+        <v>6.633947858808095</v>
       </c>
       <c r="E36">
-        <v>1.43416</v>
+        <v>1.5044</v>
       </c>
       <c r="F36">
-        <v>2.38816</v>
+        <v>2.4584</v>
       </c>
       <c r="G36">
         <v>1.14</v>
@@ -4233,28 +4233,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M36">
-        <v>0.132065248</v>
+        <v>0.13594952</v>
       </c>
       <c r="N36">
-        <v>0.5999755683265307</v>
+        <v>0.5960912963265306</v>
       </c>
       <c r="O36">
-        <v>0.1799926704979592</v>
+        <v>0.1788273888979592</v>
       </c>
       <c r="P36">
-        <v>0.4199828978285715</v>
+        <v>0.4172639074285714</v>
       </c>
       <c r="Q36">
-        <v>0.5399828978285715</v>
+        <v>0.5372639074285714</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2952401796383576</v>
+        <v>0.2982315814842861</v>
       </c>
       <c r="T36">
-        <v>1.739207323398949</v>
+        <v>1.760064700928146</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.543023826574957</v>
+        <v>5.384651717244243</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.207399027964786</v>
+        <v>0.206778137368256</v>
       </c>
       <c r="C37">
-        <v>5.315547858808094</v>
+        <v>5.270894910011089</v>
       </c>
       <c r="D37">
-        <v>6.633947858808095</v>
+        <v>6.659534910011089</v>
       </c>
       <c r="E37">
-        <v>1.5044</v>
+        <v>1.57464</v>
       </c>
       <c r="F37">
-        <v>2.4584</v>
+        <v>2.52864</v>
       </c>
       <c r="G37">
         <v>1.14</v>
@@ -4315,28 +4315,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M37">
-        <v>0.13594952</v>
+        <v>0.139833792</v>
       </c>
       <c r="N37">
-        <v>0.5960912963265306</v>
+        <v>0.5922070243265306</v>
       </c>
       <c r="O37">
-        <v>0.1788273888979592</v>
+        <v>0.1776621072979592</v>
       </c>
       <c r="P37">
-        <v>0.4172639074285714</v>
+        <v>0.4145449170285714</v>
       </c>
       <c r="Q37">
-        <v>0.5372639074285714</v>
+        <v>0.5345449170285714</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2982315814842861</v>
+        <v>0.3013164646379</v>
       </c>
       <c r="T37">
-        <v>1.760064700928146</v>
+        <v>1.781573871505132</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.384651717244243</v>
+        <v>5.235078058431903</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.206778137368256</v>
+        <v>0.206157246771726</v>
       </c>
       <c r="C38">
-        <v>5.270894910011087</v>
+        <v>5.226440103297522</v>
       </c>
       <c r="D38">
-        <v>6.659534910011088</v>
+        <v>6.685320103297522</v>
       </c>
       <c r="E38">
-        <v>1.57464</v>
+        <v>1.64488</v>
       </c>
       <c r="F38">
-        <v>2.52864</v>
+        <v>2.59888</v>
       </c>
       <c r="G38">
         <v>1.14</v>
@@ -4397,28 +4397,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M38">
-        <v>0.139833792</v>
+        <v>0.143718064</v>
       </c>
       <c r="N38">
-        <v>0.5922070243265306</v>
+        <v>0.5883227523265306</v>
       </c>
       <c r="O38">
-        <v>0.1776621072979592</v>
+        <v>0.1764968256979592</v>
       </c>
       <c r="P38">
-        <v>0.4145449170285714</v>
+        <v>0.4118259266285714</v>
       </c>
       <c r="Q38">
-        <v>0.5345449170285714</v>
+        <v>0.5318259266285714</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.3013164646379</v>
+        <v>0.3044992805900412</v>
       </c>
       <c r="T38">
-        <v>1.781573871505132</v>
+        <v>1.803765872894084</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.235078058431903</v>
+        <v>5.093589462258068</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.206157246771726</v>
+        <v>0.2055363561751959</v>
       </c>
       <c r="C39">
-        <v>5.226440103297522</v>
+        <v>5.182185749185038</v>
       </c>
       <c r="D39">
-        <v>6.685320103297522</v>
+        <v>6.711305749185038</v>
       </c>
       <c r="E39">
-        <v>1.64488</v>
+        <v>1.71512</v>
       </c>
       <c r="F39">
-        <v>2.59888</v>
+        <v>2.66912</v>
       </c>
       <c r="G39">
         <v>1.14</v>
@@ -4479,28 +4479,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M39">
-        <v>0.143718064</v>
+        <v>0.147602336</v>
       </c>
       <c r="N39">
-        <v>0.5883227523265306</v>
+        <v>0.5844384803265306</v>
       </c>
       <c r="O39">
-        <v>0.1764968256979592</v>
+        <v>0.1753315440979592</v>
       </c>
       <c r="P39">
-        <v>0.4118259266285714</v>
+        <v>0.4091069362285714</v>
       </c>
       <c r="Q39">
-        <v>0.5318259266285714</v>
+        <v>0.5291069362285714</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.3044992805900412</v>
+        <v>0.3077847680245096</v>
       </c>
       <c r="T39">
-        <v>1.803765872894084</v>
+        <v>1.826673745295584</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.093589462258068</v>
+        <v>4.959547634303908</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2055363561751959</v>
+        <v>0.2049154655786659</v>
       </c>
       <c r="C40">
-        <v>5.182185749185038</v>
+        <v>5.138134194255114</v>
       </c>
       <c r="D40">
-        <v>6.711305749185038</v>
+        <v>6.737494194255115</v>
       </c>
       <c r="E40">
-        <v>1.71512</v>
+        <v>1.78536</v>
       </c>
       <c r="F40">
-        <v>2.66912</v>
+        <v>2.73936</v>
       </c>
       <c r="G40">
         <v>1.14</v>
@@ -4561,28 +4561,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M40">
-        <v>0.147602336</v>
+        <v>0.151486608</v>
       </c>
       <c r="N40">
-        <v>0.5844384803265306</v>
+        <v>0.5805542083265306</v>
       </c>
       <c r="O40">
-        <v>0.1753315440979592</v>
+        <v>0.1741662624979592</v>
       </c>
       <c r="P40">
-        <v>0.4091069362285714</v>
+        <v>0.4063879458285714</v>
       </c>
       <c r="Q40">
-        <v>0.5291069362285714</v>
+        <v>0.5263879458285714</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.3077847680245096</v>
+        <v>0.3111779763584688</v>
       </c>
       <c r="T40">
-        <v>1.826673745295584</v>
+        <v>1.850332695480739</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.959547634303908</v>
+        <v>4.832379746244834</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2049154655786659</v>
+        <v>0.204294574982136</v>
       </c>
       <c r="C41">
-        <v>5.138134194255114</v>
+        <v>5.094287821859465</v>
       </c>
       <c r="D41">
-        <v>6.737494194255115</v>
+        <v>6.763887821859465</v>
       </c>
       <c r="E41">
-        <v>1.78536</v>
+        <v>1.8556</v>
       </c>
       <c r="F41">
-        <v>2.73936</v>
+        <v>2.8096</v>
       </c>
       <c r="G41">
         <v>1.14</v>
@@ -4643,28 +4643,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M41">
-        <v>0.151486608</v>
+        <v>0.15537088</v>
       </c>
       <c r="N41">
-        <v>0.5805542083265306</v>
+        <v>0.5766699363265306</v>
       </c>
       <c r="O41">
-        <v>0.1741662624979592</v>
+        <v>0.1730009808979592</v>
       </c>
       <c r="P41">
-        <v>0.4063879458285714</v>
+        <v>0.4036689554285715</v>
       </c>
       <c r="Q41">
-        <v>0.5263879458285714</v>
+        <v>0.5236689554285714</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.3111779763584688</v>
+        <v>0.3146842916368933</v>
       </c>
       <c r="T41">
-        <v>1.850332695480739</v>
+        <v>1.874780277338733</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.832379746244834</v>
+        <v>4.711570252588713</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.204294574982136</v>
+        <v>0.2036736843856059</v>
       </c>
       <c r="C42">
-        <v>5.094287821859465</v>
+        <v>5.050649052843085</v>
       </c>
       <c r="D42">
-        <v>6.763887821859465</v>
+        <v>6.790489052843085</v>
       </c>
       <c r="E42">
-        <v>1.8556</v>
+        <v>1.92584</v>
       </c>
       <c r="F42">
-        <v>2.8096</v>
+        <v>2.87984</v>
       </c>
       <c r="G42">
         <v>1.14</v>
@@ -4725,28 +4725,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M42">
-        <v>0.15537088</v>
+        <v>0.159255152</v>
       </c>
       <c r="N42">
-        <v>0.5766699363265306</v>
+        <v>0.5727856643265306</v>
       </c>
       <c r="O42">
-        <v>0.1730009808979592</v>
+        <v>0.1718356992979592</v>
       </c>
       <c r="P42">
-        <v>0.4036689554285715</v>
+        <v>0.4009499650285714</v>
       </c>
       <c r="Q42">
-        <v>0.5236689554285714</v>
+        <v>0.5209499650285714</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.3146842916368933</v>
+        <v>0.3183094650603491</v>
       </c>
       <c r="T42">
-        <v>1.874780277338733</v>
+        <v>1.900056590785134</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.711570252588713</v>
+        <v>4.596653904964597</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2036736843856059</v>
+        <v>0.2037877937890759</v>
       </c>
       <c r="C43">
-        <v>5.050649052843085</v>
+        <v>4.975504505241615</v>
       </c>
       <c r="D43">
-        <v>6.790489052843085</v>
+        <v>6.785584505241616</v>
       </c>
       <c r="E43">
-        <v>1.92584</v>
+        <v>1.99608</v>
       </c>
       <c r="F43">
-        <v>2.87984</v>
+        <v>2.95008</v>
       </c>
       <c r="G43">
         <v>1.14</v>
@@ -4807,45 +4807,45 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M43">
-        <v>0.159255152</v>
+        <v>0.170514624</v>
       </c>
       <c r="N43">
-        <v>0.5727856643265306</v>
+        <v>0.5615261923265306</v>
       </c>
       <c r="O43">
-        <v>0.1718356992979592</v>
+        <v>0.1684578576979592</v>
       </c>
       <c r="P43">
-        <v>0.4009499650285714</v>
+        <v>0.3930683346285714</v>
       </c>
       <c r="Q43">
-        <v>0.5209499650285714</v>
+        <v>0.5130683346285714</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.3183094650603491</v>
+        <v>0.322059644463924</v>
       </c>
       <c r="T43">
-        <v>1.900056590785134</v>
+        <v>1.926204501246928</v>
       </c>
       <c r="U43">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V43">
         <v>0.3</v>
       </c>
       <c r="W43">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.596653904964597</v>
+        <v>4.293126297053151</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2037877937890759</v>
+        <v>0.2031844031925459</v>
       </c>
       <c r="C44">
-        <v>4.975504505241617</v>
+        <v>4.931279521973696</v>
       </c>
       <c r="D44">
-        <v>6.785584505241617</v>
+        <v>6.811599521973696</v>
       </c>
       <c r="E44">
-        <v>1.99608</v>
+        <v>2.06632</v>
       </c>
       <c r="F44">
-        <v>2.95008</v>
+        <v>3.02032</v>
       </c>
       <c r="G44">
         <v>1.14</v>
@@ -4889,28 +4889,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M44">
-        <v>0.170514624</v>
+        <v>0.174574496</v>
       </c>
       <c r="N44">
-        <v>0.5615261923265307</v>
+        <v>0.5574663203265307</v>
       </c>
       <c r="O44">
-        <v>0.1684578576979592</v>
+        <v>0.1672398960979592</v>
       </c>
       <c r="P44">
-        <v>0.3930683346285715</v>
+        <v>0.3902264242285715</v>
       </c>
       <c r="Q44">
-        <v>0.5130683346285715</v>
+        <v>0.5102264242285715</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.322059644463924</v>
+        <v>0.3259414091097297</v>
       </c>
       <c r="T44">
-        <v>1.926204501246927</v>
+        <v>1.95326988225124</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.293126297053153</v>
+        <v>4.193286150610056</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2031844031925459</v>
+        <v>0.2025810125960159</v>
       </c>
       <c r="C45">
-        <v>4.931279521973696</v>
+        <v>4.887254782551697</v>
       </c>
       <c r="D45">
-        <v>6.811599521973696</v>
+        <v>6.837814782551697</v>
       </c>
       <c r="E45">
-        <v>2.06632</v>
+        <v>2.13656</v>
       </c>
       <c r="F45">
-        <v>3.02032</v>
+        <v>3.09056</v>
       </c>
       <c r="G45">
         <v>1.14</v>
@@ -4971,28 +4971,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M45">
-        <v>0.174574496</v>
+        <v>0.178634368</v>
       </c>
       <c r="N45">
-        <v>0.5574663203265307</v>
+        <v>0.5534064483265306</v>
       </c>
       <c r="O45">
-        <v>0.1672398960979592</v>
+        <v>0.1660219344979592</v>
       </c>
       <c r="P45">
-        <v>0.3902264242285715</v>
+        <v>0.3873845138285714</v>
       </c>
       <c r="Q45">
-        <v>0.5102264242285715</v>
+        <v>0.5073845138285714</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.3259414091097297</v>
+        <v>0.3299618082071712</v>
       </c>
       <c r="T45">
-        <v>1.95326988225124</v>
+        <v>1.981301884005707</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.193286150610056</v>
+        <v>4.097984192641645</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2025810125960159</v>
+        <v>0.2019776219994859</v>
       </c>
       <c r="C46">
-        <v>4.887254782551697</v>
+        <v>4.843432607895579</v>
       </c>
       <c r="D46">
-        <v>6.837814782551697</v>
+        <v>6.86423260789558</v>
       </c>
       <c r="E46">
-        <v>2.13656</v>
+        <v>2.2068</v>
       </c>
       <c r="F46">
-        <v>3.09056</v>
+        <v>3.1608</v>
       </c>
       <c r="G46">
         <v>1.14</v>
@@ -5053,28 +5053,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M46">
-        <v>0.178634368</v>
+        <v>0.18269424</v>
       </c>
       <c r="N46">
-        <v>0.5534064483265306</v>
+        <v>0.5493465763265306</v>
       </c>
       <c r="O46">
-        <v>0.1660219344979592</v>
+        <v>0.1648039728979592</v>
       </c>
       <c r="P46">
-        <v>0.3873845138285714</v>
+        <v>0.3845426034285714</v>
       </c>
       <c r="Q46">
-        <v>0.5073845138285714</v>
+        <v>0.5045426034285714</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.3299618082071712</v>
+        <v>0.3341284036354289</v>
       </c>
       <c r="T46">
-        <v>1.981301884005707</v>
+        <v>2.010353231278518</v>
       </c>
       <c r="U46">
         <v>0.0578</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.097984192641645</v>
+        <v>4.006917877249609</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2019776219994859</v>
+        <v>0.2025012314029559</v>
       </c>
       <c r="C47">
-        <v>4.843432607895579</v>
+        <v>4.750256114615214</v>
       </c>
       <c r="D47">
-        <v>6.86423260789558</v>
+        <v>6.841296114615214</v>
       </c>
       <c r="E47">
-        <v>2.2068</v>
+        <v>2.27704</v>
       </c>
       <c r="F47">
-        <v>3.1608</v>
+        <v>3.23104</v>
       </c>
       <c r="G47">
         <v>1.14</v>
@@ -5135,45 +5135,45 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M47">
-        <v>0.18269424</v>
+        <v>0.198062752</v>
       </c>
       <c r="N47">
-        <v>0.5493465763265306</v>
+        <v>0.5339780643265306</v>
       </c>
       <c r="O47">
-        <v>0.1648039728979592</v>
+        <v>0.1601934192979592</v>
       </c>
       <c r="P47">
-        <v>0.3845426034285714</v>
+        <v>0.3737846450285714</v>
       </c>
       <c r="Q47">
-        <v>0.5045426034285714</v>
+        <v>0.4937846450285714</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.3341284036354289</v>
+        <v>0.3384493174128812</v>
       </c>
       <c r="T47">
-        <v>2.010353231278518</v>
+        <v>2.040480554376247</v>
       </c>
       <c r="U47">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V47">
         <v>0.3</v>
       </c>
       <c r="W47">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.006917877249609</v>
+        <v>3.696004467950292</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2025012314029559</v>
+        <v>0.2019223408064259</v>
       </c>
       <c r="C48">
-        <v>4.750256114615214</v>
+        <v>4.705383156694976</v>
       </c>
       <c r="D48">
-        <v>6.841296114615214</v>
+        <v>6.866663156694976</v>
       </c>
       <c r="E48">
-        <v>2.27704</v>
+        <v>2.34728</v>
       </c>
       <c r="F48">
-        <v>3.23104</v>
+        <v>3.30128</v>
       </c>
       <c r="G48">
         <v>1.14</v>
@@ -5217,28 +5217,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M48">
-        <v>0.198062752</v>
+        <v>0.202368464</v>
       </c>
       <c r="N48">
-        <v>0.5339780643265306</v>
+        <v>0.5296723523265305</v>
       </c>
       <c r="O48">
-        <v>0.1601934192979592</v>
+        <v>0.1589017056979592</v>
       </c>
       <c r="P48">
-        <v>0.3737846450285714</v>
+        <v>0.3707706466285714</v>
       </c>
       <c r="Q48">
-        <v>0.4937846450285714</v>
+        <v>0.4907706466285714</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.3384493174128812</v>
+        <v>0.3429332845404262</v>
       </c>
       <c r="T48">
-        <v>2.040480554376247</v>
+        <v>2.071744757590873</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.696004467950292</v>
+        <v>3.617366075015179</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2019223408064259</v>
+        <v>0.2013434502098959</v>
       </c>
       <c r="C49">
-        <v>4.705383156694976</v>
+        <v>4.660699017295894</v>
       </c>
       <c r="D49">
-        <v>6.866663156694976</v>
+        <v>6.892219017295894</v>
       </c>
       <c r="E49">
-        <v>2.34728</v>
+        <v>2.417520000000001</v>
       </c>
       <c r="F49">
-        <v>3.30128</v>
+        <v>3.37152</v>
       </c>
       <c r="G49">
         <v>1.14</v>
@@ -5299,28 +5299,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M49">
-        <v>0.202368464</v>
+        <v>0.206674176</v>
       </c>
       <c r="N49">
-        <v>0.5296723523265305</v>
+        <v>0.5253666403265306</v>
       </c>
       <c r="O49">
-        <v>0.1589017056979592</v>
+        <v>0.1576099920979592</v>
       </c>
       <c r="P49">
-        <v>0.3707706466285714</v>
+        <v>0.3677566482285714</v>
       </c>
       <c r="Q49">
-        <v>0.4907706466285714</v>
+        <v>0.4877566482285714</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.3429332845404262</v>
+        <v>0.3475897119421075</v>
       </c>
       <c r="T49">
-        <v>2.071744757590873</v>
+        <v>2.104211430159907</v>
       </c>
       <c r="U49">
         <v>0.0613</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.617366075015179</v>
+        <v>3.542004281785696</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2013434502098959</v>
+        <v>0.2017249596133658</v>
       </c>
       <c r="C50">
-        <v>4.660699017295894</v>
+        <v>4.573595480038017</v>
       </c>
       <c r="D50">
-        <v>6.892219017295894</v>
+        <v>6.875355480038017</v>
       </c>
       <c r="E50">
-        <v>2.41752</v>
+        <v>2.48776</v>
       </c>
       <c r="F50">
-        <v>3.37152</v>
+        <v>3.44176</v>
       </c>
       <c r="G50">
         <v>1.14</v>
@@ -5381,45 +5381,45 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M50">
-        <v>0.206674176</v>
+        <v>0.220616816</v>
       </c>
       <c r="N50">
-        <v>0.5253666403265307</v>
+        <v>0.5114240003265306</v>
       </c>
       <c r="O50">
-        <v>0.1576099920979592</v>
+        <v>0.1534272000979592</v>
       </c>
       <c r="P50">
-        <v>0.3677566482285715</v>
+        <v>0.3579968002285714</v>
       </c>
       <c r="Q50">
-        <v>0.4877566482285715</v>
+        <v>0.4779968002285714</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.3475897119421075</v>
+        <v>0.352428744339933</v>
       </c>
       <c r="T50">
-        <v>2.104211430159907</v>
+        <v>2.137951305574785</v>
       </c>
       <c r="U50">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V50">
         <v>0.3</v>
       </c>
       <c r="W50">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.542004281785697</v>
+        <v>3.318155114370477</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2017249596133658</v>
+        <v>0.2011656690168359</v>
       </c>
       <c r="C51">
-        <v>4.573595480038017</v>
+        <v>4.528105617517678</v>
       </c>
       <c r="D51">
-        <v>6.875355480038017</v>
+        <v>6.900105617517678</v>
       </c>
       <c r="E51">
-        <v>2.48776</v>
+        <v>2.558</v>
       </c>
       <c r="F51">
-        <v>3.44176</v>
+        <v>3.512</v>
       </c>
       <c r="G51">
         <v>1.14</v>
@@ -5463,28 +5463,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M51">
-        <v>0.220616816</v>
+        <v>0.2251192</v>
       </c>
       <c r="N51">
-        <v>0.5114240003265306</v>
+        <v>0.5069216163265307</v>
       </c>
       <c r="O51">
-        <v>0.1534272000979592</v>
+        <v>0.1520764848979592</v>
       </c>
       <c r="P51">
-        <v>0.3579968002285714</v>
+        <v>0.3548451314285714</v>
       </c>
       <c r="Q51">
-        <v>0.4779968002285714</v>
+        <v>0.4748451314285714</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.352428744339933</v>
+        <v>0.3574613380336717</v>
       </c>
       <c r="T51">
-        <v>2.137951305574785</v>
+        <v>2.173040776006259</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.318155114370477</v>
+        <v>3.251792012083068</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2011656690168359</v>
+        <v>0.2006063784203059</v>
       </c>
       <c r="C52">
-        <v>4.528105617517678</v>
+        <v>4.482794591545243</v>
       </c>
       <c r="D52">
-        <v>6.900105617517678</v>
+        <v>6.925034591545243</v>
       </c>
       <c r="E52">
-        <v>2.558</v>
+        <v>2.62824</v>
       </c>
       <c r="F52">
-        <v>3.512</v>
+        <v>3.58224</v>
       </c>
       <c r="G52">
         <v>1.14</v>
@@ -5545,28 +5545,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M52">
-        <v>0.2251192</v>
+        <v>0.229621584</v>
       </c>
       <c r="N52">
-        <v>0.5069216163265307</v>
+        <v>0.5024192323265306</v>
       </c>
       <c r="O52">
-        <v>0.1520764848979592</v>
+        <v>0.1507257696979592</v>
       </c>
       <c r="P52">
-        <v>0.3548451314285714</v>
+        <v>0.3516934626285715</v>
       </c>
       <c r="Q52">
-        <v>0.4748451314285714</v>
+        <v>0.4716934626285715</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3574613380336717</v>
+        <v>0.3626993437149099</v>
       </c>
       <c r="T52">
-        <v>2.173040776006259</v>
+        <v>2.20956246972065</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.251792012083068</v>
+        <v>3.188031384395165</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2006063784203059</v>
+        <v>0.2000470878237759</v>
       </c>
       <c r="C53">
-        <v>4.482794591545243</v>
+        <v>4.437664347472182</v>
       </c>
       <c r="D53">
-        <v>6.925034591545243</v>
+        <v>6.950144347472183</v>
       </c>
       <c r="E53">
-        <v>2.62824</v>
+        <v>2.69848</v>
       </c>
       <c r="F53">
-        <v>3.58224</v>
+        <v>3.65248</v>
       </c>
       <c r="G53">
         <v>1.14</v>
@@ -5627,28 +5627,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M53">
-        <v>0.229621584</v>
+        <v>0.234123968</v>
       </c>
       <c r="N53">
-        <v>0.5024192323265306</v>
+        <v>0.4979168483265306</v>
       </c>
       <c r="O53">
-        <v>0.1507257696979592</v>
+        <v>0.1493750544979592</v>
       </c>
       <c r="P53">
-        <v>0.3516934626285715</v>
+        <v>0.3485417938285714</v>
       </c>
       <c r="Q53">
-        <v>0.4716934626285715</v>
+        <v>0.4685417938285714</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3626993437149099</v>
+        <v>0.3681555996328664</v>
       </c>
       <c r="T53">
-        <v>2.20956246972065</v>
+        <v>2.247605900673141</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.188031384395165</v>
+        <v>3.126723088541411</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2000470878237759</v>
+        <v>0.1994877972272458</v>
       </c>
       <c r="C54">
-        <v>4.437664347472182</v>
+        <v>4.392716858967551</v>
       </c>
       <c r="D54">
-        <v>6.950144347472183</v>
+        <v>6.975436858967552</v>
       </c>
       <c r="E54">
-        <v>2.69848</v>
+        <v>2.76872</v>
       </c>
       <c r="F54">
-        <v>3.65248</v>
+        <v>3.72272</v>
       </c>
       <c r="G54">
         <v>1.14</v>
@@ -5709,28 +5709,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M54">
-        <v>0.234123968</v>
+        <v>0.238626352</v>
       </c>
       <c r="N54">
-        <v>0.4979168483265306</v>
+        <v>0.4934144643265306</v>
       </c>
       <c r="O54">
-        <v>0.1493750544979592</v>
+        <v>0.1480243392979592</v>
       </c>
       <c r="P54">
-        <v>0.3485417938285714</v>
+        <v>0.3453901250285714</v>
       </c>
       <c r="Q54">
-        <v>0.4685417938285714</v>
+        <v>0.4653901250285714</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3681555996328664</v>
+        <v>0.3738440366537145</v>
       </c>
       <c r="T54">
-        <v>2.247605900673141</v>
+        <v>2.287268201027865</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.126723088541411</v>
+        <v>3.067728313285913</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1994877972272458</v>
+        <v>0.1989285066307158</v>
       </c>
       <c r="C55">
-        <v>4.392716858967551</v>
+        <v>4.347954128535115</v>
       </c>
       <c r="D55">
-        <v>6.975436858967552</v>
+        <v>7.000914128535115</v>
       </c>
       <c r="E55">
-        <v>2.76872</v>
+        <v>2.83896</v>
       </c>
       <c r="F55">
-        <v>3.72272</v>
+        <v>3.79296</v>
       </c>
       <c r="G55">
         <v>1.14</v>
@@ -5791,28 +5791,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M55">
-        <v>0.238626352</v>
+        <v>0.243128736</v>
       </c>
       <c r="N55">
-        <v>0.4934144643265306</v>
+        <v>0.4889120803265306</v>
       </c>
       <c r="O55">
-        <v>0.1480243392979592</v>
+        <v>0.1466736240979592</v>
       </c>
       <c r="P55">
-        <v>0.3453901250285714</v>
+        <v>0.3422384562285714</v>
       </c>
       <c r="Q55">
-        <v>0.4653901250285714</v>
+        <v>0.4622384562285714</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3738440366537145</v>
+        <v>0.3797797970232953</v>
       </c>
       <c r="T55">
-        <v>2.287268201027865</v>
+        <v>2.328654949224099</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.067728313285913</v>
+        <v>3.010918529706544</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1989285066307158</v>
+        <v>0.2013722160341858</v>
       </c>
       <c r="C56">
-        <v>4.347954128535115</v>
+        <v>4.167744622893903</v>
       </c>
       <c r="D56">
-        <v>7.000914128535115</v>
+        <v>6.890944622893904</v>
       </c>
       <c r="E56">
-        <v>2.83896</v>
+        <v>2.9092</v>
       </c>
       <c r="F56">
-        <v>3.79296</v>
+        <v>3.8632</v>
       </c>
       <c r="G56">
         <v>1.14</v>
@@ -5873,45 +5873,45 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M56">
-        <v>0.243128736</v>
+        <v>0.27776408</v>
       </c>
       <c r="N56">
-        <v>0.4889120803265306</v>
+        <v>0.4542767363265306</v>
       </c>
       <c r="O56">
-        <v>0.1466736240979592</v>
+        <v>0.1362830208979592</v>
       </c>
       <c r="P56">
-        <v>0.3422384562285714</v>
+        <v>0.3179937154285714</v>
       </c>
       <c r="Q56">
-        <v>0.4622384562285714</v>
+        <v>0.4379937154285714</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3797797970232953</v>
+        <v>0.3859793689648574</v>
       </c>
       <c r="T56">
-        <v>2.328654949224099</v>
+        <v>2.371881108451277</v>
       </c>
       <c r="U56">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V56">
         <v>0.3</v>
       </c>
       <c r="W56">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>3.010918529706544</v>
+        <v>2.635476899412374</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2013722160341858</v>
+        <v>0.2008675254376558</v>
       </c>
       <c r="C57">
-        <v>4.167744622893903</v>
+        <v>4.11993223913765</v>
       </c>
       <c r="D57">
-        <v>6.890944622893904</v>
+        <v>6.913372239137652</v>
       </c>
       <c r="E57">
-        <v>2.9092</v>
+        <v>2.97944</v>
       </c>
       <c r="F57">
-        <v>3.8632</v>
+        <v>3.93344</v>
       </c>
       <c r="G57">
         <v>1.14</v>
@@ -5955,28 +5955,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M57">
-        <v>0.27776408</v>
+        <v>0.2828143360000001</v>
       </c>
       <c r="N57">
-        <v>0.4542767363265306</v>
+        <v>0.4492264803265306</v>
       </c>
       <c r="O57">
-        <v>0.1362830208979592</v>
+        <v>0.1347679440979592</v>
       </c>
       <c r="P57">
-        <v>0.3179937154285714</v>
+        <v>0.3144585362285714</v>
       </c>
       <c r="Q57">
-        <v>0.4379937154285714</v>
+        <v>0.4344585362285714</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3859793689648574</v>
+        <v>0.3924607396310359</v>
       </c>
       <c r="T57">
-        <v>2.371881108451277</v>
+        <v>2.417072093097871</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.635476899412374</v>
+        <v>2.588414811922867</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2008675254376558</v>
+        <v>0.2003628348411258</v>
       </c>
       <c r="C58">
-        <v>4.11993223913765</v>
+        <v>4.072266320177191</v>
       </c>
       <c r="D58">
-        <v>6.913372239137652</v>
+        <v>6.935946320177192</v>
       </c>
       <c r="E58">
-        <v>2.97944</v>
+        <v>3.04968</v>
       </c>
       <c r="F58">
-        <v>3.93344</v>
+        <v>4.00368</v>
       </c>
       <c r="G58">
         <v>1.14</v>
@@ -6037,28 +6037,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M58">
-        <v>0.2828143360000001</v>
+        <v>0.287864592</v>
       </c>
       <c r="N58">
-        <v>0.4492264803265306</v>
+        <v>0.4441762243265306</v>
       </c>
       <c r="O58">
-        <v>0.1347679440979592</v>
+        <v>0.1332528672979592</v>
       </c>
       <c r="P58">
-        <v>0.3144585362285714</v>
+        <v>0.3109233570285714</v>
       </c>
       <c r="Q58">
-        <v>0.4344585362285714</v>
+        <v>0.4309233570285714</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3924607396310359</v>
+        <v>0.399243569397967</v>
       </c>
       <c r="T58">
-        <v>2.417072093097871</v>
+        <v>2.464364984007098</v>
       </c>
       <c r="U58">
         <v>0.07190000000000001</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.588414811922867</v>
+        <v>2.543004025748782</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2003628348411258</v>
+        <v>0.2014415442445958</v>
       </c>
       <c r="C59">
-        <v>4.072266320177191</v>
+        <v>3.953955154127978</v>
       </c>
       <c r="D59">
-        <v>6.935946320177192</v>
+        <v>6.887875154127978</v>
       </c>
       <c r="E59">
-        <v>3.04968</v>
+        <v>3.11992</v>
       </c>
       <c r="F59">
-        <v>4.00368</v>
+        <v>4.07392</v>
       </c>
       <c r="G59">
         <v>1.14</v>
@@ -6119,45 +6119,45 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M59">
-        <v>0.287864592</v>
+        <v>0.308803136</v>
       </c>
       <c r="N59">
-        <v>0.4441762243265306</v>
+        <v>0.4232376803265306</v>
       </c>
       <c r="O59">
-        <v>0.1332528672979592</v>
+        <v>0.1269713040979592</v>
       </c>
       <c r="P59">
-        <v>0.3109233570285714</v>
+        <v>0.2962663762285714</v>
       </c>
       <c r="Q59">
-        <v>0.4309233570285714</v>
+        <v>0.4162663762285714</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.399243569397967</v>
+        <v>0.4063493910585614</v>
       </c>
       <c r="T59">
-        <v>2.464364984007098</v>
+        <v>2.513909917340575</v>
       </c>
       <c r="U59">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V59">
         <v>0.3</v>
       </c>
       <c r="W59">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.543004025748782</v>
+        <v>2.370574424239431</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2014415442445958</v>
+        <v>0.2009641536480657</v>
       </c>
       <c r="C60">
-        <v>3.953955154127978</v>
+        <v>3.904906948439642</v>
       </c>
       <c r="D60">
-        <v>6.887875154127978</v>
+        <v>6.909066948439642</v>
       </c>
       <c r="E60">
-        <v>3.11992</v>
+        <v>3.19016</v>
       </c>
       <c r="F60">
-        <v>4.073919999999999</v>
+        <v>4.144159999999999</v>
       </c>
       <c r="G60">
         <v>1.14</v>
@@ -6201,28 +6201,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M60">
-        <v>0.308803136</v>
+        <v>0.314127328</v>
       </c>
       <c r="N60">
-        <v>0.4232376803265306</v>
+        <v>0.4179134883265306</v>
       </c>
       <c r="O60">
-        <v>0.1269713040979592</v>
+        <v>0.1253740464979592</v>
       </c>
       <c r="P60">
-        <v>0.2962663762285714</v>
+        <v>0.2925394418285714</v>
       </c>
       <c r="Q60">
-        <v>0.4162663762285714</v>
+        <v>0.4125394418285714</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.4063493910585613</v>
+        <v>0.413801838166014</v>
       </c>
       <c r="T60">
-        <v>2.513909917340574</v>
+        <v>2.565871676690317</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.370574424239431</v>
+        <v>2.330395196709949</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2009641536480657</v>
+        <v>0.2004867630515358</v>
       </c>
       <c r="C61">
-        <v>3.904906948439642</v>
+        <v>3.855989545971029</v>
       </c>
       <c r="D61">
-        <v>6.909066948439642</v>
+        <v>6.930389545971029</v>
       </c>
       <c r="E61">
-        <v>3.19016</v>
+        <v>3.2604</v>
       </c>
       <c r="F61">
-        <v>4.144159999999999</v>
+        <v>4.214399999999999</v>
       </c>
       <c r="G61">
         <v>1.14</v>
@@ -6283,28 +6283,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M61">
-        <v>0.314127328</v>
+        <v>0.31945152</v>
       </c>
       <c r="N61">
-        <v>0.4179134883265306</v>
+        <v>0.4125892963265306</v>
       </c>
       <c r="O61">
-        <v>0.1253740464979592</v>
+        <v>0.1237767888979592</v>
       </c>
       <c r="P61">
-        <v>0.2925394418285714</v>
+        <v>0.2888125074285715</v>
       </c>
       <c r="Q61">
-        <v>0.4125394418285714</v>
+        <v>0.4088125074285714</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.413801838166014</v>
+        <v>0.4216269076288394</v>
       </c>
       <c r="T61">
-        <v>2.565871676690317</v>
+        <v>2.620431524007548</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.330395196709949</v>
+        <v>2.291555276764783</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2004867630515358</v>
+        <v>0.2000093724550057</v>
       </c>
       <c r="C62">
-        <v>3.855989545971029</v>
+        <v>3.807204161516541</v>
       </c>
       <c r="D62">
-        <v>6.930389545971029</v>
+        <v>6.951844161516541</v>
       </c>
       <c r="E62">
-        <v>3.2604</v>
+        <v>3.33064</v>
       </c>
       <c r="F62">
-        <v>4.214399999999999</v>
+        <v>4.28464</v>
       </c>
       <c r="G62">
         <v>1.14</v>
@@ -6365,28 +6365,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M62">
-        <v>0.31945152</v>
+        <v>0.324775712</v>
       </c>
       <c r="N62">
-        <v>0.4125892963265306</v>
+        <v>0.4072651043265306</v>
       </c>
       <c r="O62">
-        <v>0.1237767888979592</v>
+        <v>0.1221795312979592</v>
       </c>
       <c r="P62">
-        <v>0.2888125074285715</v>
+        <v>0.2850855730285715</v>
       </c>
       <c r="Q62">
-        <v>0.4088125074285714</v>
+        <v>0.4050855730285715</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.4216269076288394</v>
+        <v>0.4298532627051429</v>
       </c>
       <c r="T62">
-        <v>2.620431524007548</v>
+        <v>2.677789312212841</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.291555276764783</v>
+        <v>2.253988796817819</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2000093724550057</v>
+        <v>0.1995319818584758</v>
       </c>
       <c r="C63">
-        <v>3.807204161516541</v>
+        <v>3.758552024959981</v>
       </c>
       <c r="D63">
-        <v>6.951844161516541</v>
+        <v>6.97343202495998</v>
       </c>
       <c r="E63">
-        <v>3.33064</v>
+        <v>3.40088</v>
       </c>
       <c r="F63">
-        <v>4.28464</v>
+        <v>4.35488</v>
       </c>
       <c r="G63">
         <v>1.14</v>
@@ -6447,28 +6447,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M63">
-        <v>0.324775712</v>
+        <v>0.330099904</v>
       </c>
       <c r="N63">
-        <v>0.4072651043265306</v>
+        <v>0.4019409123265306</v>
       </c>
       <c r="O63">
-        <v>0.1221795312979592</v>
+        <v>0.1205822736979592</v>
       </c>
       <c r="P63">
-        <v>0.2850855730285715</v>
+        <v>0.2813586386285715</v>
       </c>
       <c r="Q63">
-        <v>0.4050855730285715</v>
+        <v>0.4013586386285715</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.4298532627051429</v>
+        <v>0.438512583838094</v>
       </c>
       <c r="T63">
-        <v>2.677789312212841</v>
+        <v>2.738165931376308</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.253988796817819</v>
+        <v>2.217634138804629</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1995319818584758</v>
+        <v>0.1990545912619457</v>
       </c>
       <c r="C64">
-        <v>3.758552024959981</v>
+        <v>3.710034381509592</v>
       </c>
       <c r="D64">
-        <v>6.97343202495998</v>
+        <v>6.995154381509592</v>
       </c>
       <c r="E64">
-        <v>3.40088</v>
+        <v>3.47112</v>
       </c>
       <c r="F64">
-        <v>4.35488</v>
+        <v>4.42512</v>
       </c>
       <c r="G64">
         <v>1.14</v>
@@ -6529,28 +6529,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M64">
-        <v>0.330099904</v>
+        <v>0.335424096</v>
       </c>
       <c r="N64">
-        <v>0.4019409123265306</v>
+        <v>0.3966167203265306</v>
       </c>
       <c r="O64">
-        <v>0.1205822736979592</v>
+        <v>0.1189850160979592</v>
       </c>
       <c r="P64">
-        <v>0.2813586386285715</v>
+        <v>0.2776317042285714</v>
       </c>
       <c r="Q64">
-        <v>0.4013586386285715</v>
+        <v>0.3976317042285714</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.438512583838094</v>
+        <v>0.4476399763836372</v>
       </c>
       <c r="T64">
-        <v>2.738165931376308</v>
+        <v>2.801806151575638</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.217634138804629</v>
+        <v>2.182433596918841</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1990545912619457</v>
+        <v>0.1985772006654157</v>
       </c>
       <c r="C65">
-        <v>3.710034381509592</v>
+        <v>3.661652491937481</v>
       </c>
       <c r="D65">
-        <v>6.995154381509592</v>
+        <v>7.01701249193748</v>
       </c>
       <c r="E65">
-        <v>3.47112</v>
+        <v>3.54136</v>
       </c>
       <c r="F65">
-        <v>4.42512</v>
+        <v>4.49536</v>
       </c>
       <c r="G65">
         <v>1.14</v>
@@ -6611,28 +6611,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M65">
-        <v>0.335424096</v>
+        <v>0.340748288</v>
       </c>
       <c r="N65">
-        <v>0.3966167203265306</v>
+        <v>0.3912925283265306</v>
       </c>
       <c r="O65">
-        <v>0.1189850160979592</v>
+        <v>0.1173877584979592</v>
       </c>
       <c r="P65">
-        <v>0.2776317042285714</v>
+        <v>0.2739047698285714</v>
       </c>
       <c r="Q65">
-        <v>0.3976317042285714</v>
+        <v>0.3939047698285714</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.4476399763836372</v>
+        <v>0.4572744462928215</v>
       </c>
       <c r="T65">
-        <v>2.801806151575638</v>
+        <v>2.868981939563819</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.182433596918841</v>
+        <v>2.148333071966984</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1985772006654157</v>
+        <v>0.1980998100688857</v>
       </c>
       <c r="C66">
-        <v>3.661652491937481</v>
+        <v>3.613407632823536</v>
       </c>
       <c r="D66">
-        <v>7.01701249193748</v>
+        <v>7.039007632823536</v>
       </c>
       <c r="E66">
-        <v>3.54136</v>
+        <v>3.6116</v>
       </c>
       <c r="F66">
-        <v>4.49536</v>
+        <v>4.5656</v>
       </c>
       <c r="G66">
         <v>1.14</v>
@@ -6693,28 +6693,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M66">
-        <v>0.340748288</v>
+        <v>0.34607248</v>
       </c>
       <c r="N66">
-        <v>0.3912925283265306</v>
+        <v>0.3859683363265306</v>
       </c>
       <c r="O66">
-        <v>0.1173877584979592</v>
+        <v>0.1157905008979592</v>
       </c>
       <c r="P66">
-        <v>0.2739047698285714</v>
+        <v>0.2701778354285714</v>
       </c>
       <c r="Q66">
-        <v>0.3939047698285714</v>
+        <v>0.3901778354285714</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.4572744462928215</v>
+        <v>0.4674594573396734</v>
       </c>
       <c r="T66">
-        <v>2.868981939563819</v>
+        <v>2.939996344008468</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.148333071966984</v>
+        <v>2.115281793936723</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1980998100688857</v>
+        <v>0.1976224194723557</v>
       </c>
       <c r="C67">
-        <v>3.613407632823536</v>
+        <v>3.565301096803964</v>
       </c>
       <c r="D67">
-        <v>7.039007632823536</v>
+        <v>7.061141096803963</v>
       </c>
       <c r="E67">
-        <v>3.6116</v>
+        <v>3.68184</v>
       </c>
       <c r="F67">
-        <v>4.5656</v>
+        <v>4.63584</v>
       </c>
       <c r="G67">
         <v>1.14</v>
@@ -6775,28 +6775,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M67">
-        <v>0.34607248</v>
+        <v>0.351396672</v>
       </c>
       <c r="N67">
-        <v>0.3859683363265306</v>
+        <v>0.3806441443265306</v>
       </c>
       <c r="O67">
-        <v>0.1157905008979592</v>
+        <v>0.1141932432979592</v>
       </c>
       <c r="P67">
-        <v>0.2701778354285714</v>
+        <v>0.2664509010285714</v>
       </c>
       <c r="Q67">
-        <v>0.3901778354285714</v>
+        <v>0.3864509010285714</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.4674594573396734</v>
+        <v>0.4782435866833992</v>
       </c>
       <c r="T67">
-        <v>2.939996344008468</v>
+        <v>3.015188066361626</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.115281793936723</v>
+        <v>2.083232069786166</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1976224194723557</v>
+        <v>0.1971450288758257</v>
       </c>
       <c r="C68">
-        <v>3.565301096803964</v>
+        <v>3.517334192824524</v>
       </c>
       <c r="D68">
-        <v>7.061141096803963</v>
+        <v>7.083414192824525</v>
       </c>
       <c r="E68">
-        <v>3.68184</v>
+        <v>3.75208</v>
       </c>
       <c r="F68">
-        <v>4.63584</v>
+        <v>4.70608</v>
       </c>
       <c r="G68">
         <v>1.14</v>
@@ -6857,28 +6857,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M68">
-        <v>0.351396672</v>
+        <v>0.356720864</v>
       </c>
       <c r="N68">
-        <v>0.3806441443265306</v>
+        <v>0.3753199523265306</v>
       </c>
       <c r="O68">
-        <v>0.1141932432979592</v>
+        <v>0.1125959856979592</v>
       </c>
       <c r="P68">
-        <v>0.2664509010285714</v>
+        <v>0.2627239666285714</v>
       </c>
       <c r="Q68">
-        <v>0.3864509010285714</v>
+        <v>0.3827239666285714</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.4782435866833992</v>
+        <v>0.4896812996237143</v>
       </c>
       <c r="T68">
-        <v>3.015188066361626</v>
+        <v>3.094936862796794</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.083232069786166</v>
+        <v>2.052139053819209</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1971450288758257</v>
+        <v>0.1966676382792957</v>
       </c>
       <c r="C69">
-        <v>3.517334192824524</v>
+        <v>3.46950824639857</v>
       </c>
       <c r="D69">
-        <v>7.083414192824525</v>
+        <v>7.105828246398571</v>
       </c>
       <c r="E69">
-        <v>3.75208</v>
+        <v>3.82232</v>
       </c>
       <c r="F69">
-        <v>4.70608</v>
+        <v>4.77632</v>
       </c>
       <c r="G69">
         <v>1.14</v>
@@ -6939,28 +6939,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M69">
-        <v>0.356720864</v>
+        <v>0.362045056</v>
       </c>
       <c r="N69">
-        <v>0.3753199523265306</v>
+        <v>0.3699957603265306</v>
       </c>
       <c r="O69">
-        <v>0.1125959856979592</v>
+        <v>0.1109987280979592</v>
       </c>
       <c r="P69">
-        <v>0.2627239666285714</v>
+        <v>0.2589970322285714</v>
       </c>
       <c r="Q69">
-        <v>0.3827239666285714</v>
+        <v>0.3789970322285714</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.4896812996237143</v>
+        <v>0.5018338696227991</v>
       </c>
       <c r="T69">
-        <v>3.094936862796794</v>
+        <v>3.179669959009159</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.052139053819209</v>
+        <v>2.021960538321867</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1966676382792957</v>
+        <v>0.2030488476827657</v>
       </c>
       <c r="C70">
-        <v>3.46950824639857</v>
+        <v>3.110911424116233</v>
       </c>
       <c r="D70">
-        <v>7.105828246398571</v>
+        <v>6.817471424116234</v>
       </c>
       <c r="E70">
-        <v>3.82232</v>
+        <v>3.89256</v>
       </c>
       <c r="F70">
-        <v>4.77632</v>
+        <v>4.84656</v>
       </c>
       <c r="G70">
         <v>1.14</v>
@@ -7021,45 +7021,45 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M70">
-        <v>0.362045056</v>
+        <v>0.4361904</v>
       </c>
       <c r="N70">
-        <v>0.3699957603265306</v>
+        <v>0.2958504163265306</v>
       </c>
       <c r="O70">
-        <v>0.1109987280979592</v>
+        <v>0.08875512489795918</v>
       </c>
       <c r="P70">
-        <v>0.2589970322285714</v>
+        <v>0.2070952914285715</v>
       </c>
       <c r="Q70">
-        <v>0.3789970322285714</v>
+        <v>0.3270952914285715</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.5018338696227991</v>
+        <v>0.5147704763960184</v>
       </c>
       <c r="T70">
-        <v>3.179669959009159</v>
+        <v>3.269869706590064</v>
       </c>
       <c r="U70">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V70">
         <v>0.3</v>
       </c>
       <c r="W70">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y70">
-        <v>2.021960538321867</v>
+        <v>1.67825980655817</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2030488476827657</v>
+        <v>0.2026708570862357</v>
       </c>
       <c r="C71">
-        <v>3.110911424116233</v>
+        <v>3.057098567680646</v>
       </c>
       <c r="D71">
-        <v>6.817471424116234</v>
+        <v>6.833898567680647</v>
       </c>
       <c r="E71">
-        <v>3.89256</v>
+        <v>3.962800000000001</v>
       </c>
       <c r="F71">
-        <v>4.84656</v>
+        <v>4.9168</v>
       </c>
       <c r="G71">
         <v>1.14</v>
@@ -7103,28 +7103,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M71">
-        <v>0.4361904</v>
+        <v>0.442512</v>
       </c>
       <c r="N71">
-        <v>0.2958504163265306</v>
+        <v>0.2895288163265306</v>
       </c>
       <c r="O71">
-        <v>0.08875512489795918</v>
+        <v>0.08685864489795918</v>
       </c>
       <c r="P71">
-        <v>0.2070952914285715</v>
+        <v>0.2026701714285714</v>
       </c>
       <c r="Q71">
-        <v>0.3270952914285715</v>
+        <v>0.3226701714285714</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.5147704763960184</v>
+        <v>0.5285695236207857</v>
       </c>
       <c r="T71">
-        <v>3.269869706590064</v>
+        <v>3.366082770676363</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.67825980655817</v>
+        <v>1.654284666464481</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2026708570862357</v>
+        <v>0.2022928664897057</v>
       </c>
       <c r="C72">
-        <v>3.057098567680646</v>
+        <v>3.003365067012953</v>
       </c>
       <c r="D72">
-        <v>6.833898567680647</v>
+        <v>6.850405067012954</v>
       </c>
       <c r="E72">
-        <v>3.962800000000001</v>
+        <v>4.033040000000001</v>
       </c>
       <c r="F72">
-        <v>4.9168</v>
+        <v>4.98704</v>
       </c>
       <c r="G72">
         <v>1.14</v>
@@ -7185,28 +7185,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M72">
-        <v>0.442512</v>
+        <v>0.4488336</v>
       </c>
       <c r="N72">
-        <v>0.2895288163265306</v>
+        <v>0.2832072163265306</v>
       </c>
       <c r="O72">
-        <v>0.08685864489795918</v>
+        <v>0.08496216489795919</v>
       </c>
       <c r="P72">
-        <v>0.2026701714285714</v>
+        <v>0.1982450514285714</v>
       </c>
       <c r="Q72">
-        <v>0.3226701714285714</v>
+        <v>0.3182450514285714</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.5285695236207857</v>
+        <v>0.5433202292748472</v>
       </c>
       <c r="T72">
-        <v>3.366082770676363</v>
+        <v>3.468931218492751</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.654284666464481</v>
+        <v>1.63098488242977</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2022928664897057</v>
+        <v>0.2019148758931756</v>
       </c>
       <c r="C73">
-        <v>3.003365067012954</v>
+        <v>2.949711498529733</v>
       </c>
       <c r="D73">
-        <v>6.850405067012954</v>
+        <v>6.866991498529732</v>
       </c>
       <c r="E73">
-        <v>4.03304</v>
+        <v>4.10328</v>
       </c>
       <c r="F73">
-        <v>4.987039999999999</v>
+        <v>5.05728</v>
       </c>
       <c r="G73">
         <v>1.14</v>
@@ -7267,28 +7267,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M73">
-        <v>0.4488335999999999</v>
+        <v>0.4551551999999999</v>
       </c>
       <c r="N73">
-        <v>0.2832072163265307</v>
+        <v>0.2768856163265307</v>
       </c>
       <c r="O73">
-        <v>0.0849621648979592</v>
+        <v>0.08306568489795921</v>
       </c>
       <c r="P73">
-        <v>0.1982450514285715</v>
+        <v>0.1938199314285715</v>
       </c>
       <c r="Q73">
-        <v>0.3182450514285715</v>
+        <v>0.3138199314285715</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.5433202292748471</v>
+        <v>0.5591245567613415</v>
       </c>
       <c r="T73">
-        <v>3.46893121849275</v>
+        <v>3.579125984010309</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.630984882429771</v>
+        <v>1.608332314618246</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2019148758931756</v>
+        <v>0.2015368852966456</v>
       </c>
       <c r="C74">
-        <v>2.949711498529733</v>
+        <v>2.896138444243664</v>
       </c>
       <c r="D74">
-        <v>6.866991498529732</v>
+        <v>6.883658444243663</v>
       </c>
       <c r="E74">
-        <v>4.10328</v>
+        <v>4.17352</v>
       </c>
       <c r="F74">
-        <v>5.05728</v>
+        <v>5.12752</v>
       </c>
       <c r="G74">
         <v>1.14</v>
@@ -7349,28 +7349,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M74">
-        <v>0.4551551999999999</v>
+        <v>0.4614768</v>
       </c>
       <c r="N74">
-        <v>0.2768856163265307</v>
+        <v>0.2705640163265307</v>
       </c>
       <c r="O74">
-        <v>0.08306568489795921</v>
+        <v>0.08116920489795919</v>
       </c>
       <c r="P74">
-        <v>0.1938199314285715</v>
+        <v>0.1893948114285715</v>
       </c>
       <c r="Q74">
-        <v>0.3138199314285715</v>
+        <v>0.3093948114285714</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.5591245567613415</v>
+        <v>0.5760995751727616</v>
       </c>
       <c r="T74">
-        <v>3.579125984010309</v>
+        <v>3.69748332475139</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.608332314618246</v>
+        <v>1.586300365102927</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2015368852966456</v>
+        <v>0.2011588947001156</v>
       </c>
       <c r="C75">
-        <v>2.896138444243664</v>
+        <v>2.842646491831611</v>
       </c>
       <c r="D75">
-        <v>6.883658444243663</v>
+        <v>6.90040649183161</v>
       </c>
       <c r="E75">
-        <v>4.17352</v>
+        <v>4.24376</v>
       </c>
       <c r="F75">
-        <v>5.12752</v>
+        <v>5.19776</v>
       </c>
       <c r="G75">
         <v>1.14</v>
@@ -7431,28 +7431,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M75">
-        <v>0.4614768</v>
+        <v>0.4677983999999999</v>
       </c>
       <c r="N75">
-        <v>0.2705640163265307</v>
+        <v>0.2642424163265307</v>
       </c>
       <c r="O75">
-        <v>0.08116920489795919</v>
+        <v>0.0792727248979592</v>
       </c>
       <c r="P75">
-        <v>0.1893948114285715</v>
+        <v>0.1849696914285715</v>
       </c>
       <c r="Q75">
-        <v>0.3093948114285714</v>
+        <v>0.3049696914285714</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.5760995751727616</v>
+        <v>0.5943803642312139</v>
       </c>
       <c r="T75">
-        <v>3.69748332475139</v>
+        <v>3.824945076318709</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.586300365102927</v>
+        <v>1.564863873682618</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2011588947001156</v>
+        <v>0.2007809041035856</v>
       </c>
       <c r="C76">
-        <v>2.842646491831611</v>
+        <v>2.789236234703698</v>
       </c>
       <c r="D76">
-        <v>6.90040649183161</v>
+        <v>6.917236234703697</v>
       </c>
       <c r="E76">
-        <v>4.24376</v>
+        <v>4.314</v>
       </c>
       <c r="F76">
-        <v>5.19776</v>
+        <v>5.268</v>
       </c>
       <c r="G76">
         <v>1.14</v>
@@ -7513,28 +7513,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M76">
-        <v>0.4677983999999999</v>
+        <v>0.47412</v>
       </c>
       <c r="N76">
-        <v>0.2642424163265307</v>
+        <v>0.2579208163265306</v>
       </c>
       <c r="O76">
-        <v>0.0792727248979592</v>
+        <v>0.07737624489795919</v>
       </c>
       <c r="P76">
-        <v>0.1849696914285715</v>
+        <v>0.1805445714285714</v>
       </c>
       <c r="Q76">
-        <v>0.3049696914285714</v>
+        <v>0.3005445714285714</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.5943803642312139</v>
+        <v>0.6141236164143424</v>
       </c>
       <c r="T76">
-        <v>3.824945076318709</v>
+        <v>3.962603768011413</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.564863873682618</v>
+        <v>1.543999022033516</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2007809041035856</v>
+        <v>0.2004029135070556</v>
       </c>
       <c r="C77">
-        <v>2.789236234703698</v>
+        <v>2.735908272073389</v>
       </c>
       <c r="D77">
-        <v>6.917236234703697</v>
+        <v>6.934148272073388</v>
       </c>
       <c r="E77">
-        <v>4.314</v>
+        <v>4.38424</v>
       </c>
       <c r="F77">
-        <v>5.268</v>
+        <v>5.33824</v>
       </c>
       <c r="G77">
         <v>1.14</v>
@@ -7595,28 +7595,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M77">
-        <v>0.47412</v>
+        <v>0.4804416</v>
       </c>
       <c r="N77">
-        <v>0.2579208163265306</v>
+        <v>0.2515992163265307</v>
       </c>
       <c r="O77">
-        <v>0.07737624489795919</v>
+        <v>0.0754797648979592</v>
       </c>
       <c r="P77">
-        <v>0.1805445714285714</v>
+        <v>0.1761194514285714</v>
       </c>
       <c r="Q77">
-        <v>0.3005445714285714</v>
+        <v>0.2961194514285714</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.6141236164143424</v>
+        <v>0.6355121396127318</v>
       </c>
       <c r="T77">
-        <v>3.962603768011413</v>
+        <v>4.111734017345177</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.543999022033516</v>
+        <v>1.523683245427812</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2004029135070556</v>
+        <v>0.2000249229105256</v>
       </c>
       <c r="C78">
-        <v>2.735908272073389</v>
+        <v>2.682663209028616</v>
       </c>
       <c r="D78">
-        <v>6.934148272073388</v>
+        <v>6.951143209028615</v>
       </c>
       <c r="E78">
-        <v>4.38424</v>
+        <v>4.45448</v>
       </c>
       <c r="F78">
-        <v>5.33824</v>
+        <v>5.40848</v>
       </c>
       <c r="G78">
         <v>1.14</v>
@@ -7677,28 +7677,28 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M78">
-        <v>0.4804416</v>
+        <v>0.4867632</v>
       </c>
       <c r="N78">
-        <v>0.2515992163265307</v>
+        <v>0.2452776163265307</v>
       </c>
       <c r="O78">
-        <v>0.0754797648979592</v>
+        <v>0.07358328489795919</v>
       </c>
       <c r="P78">
-        <v>0.1761194514285714</v>
+        <v>0.1716943314285715</v>
       </c>
       <c r="Q78">
-        <v>0.2961194514285714</v>
+        <v>0.2916943314285715</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.6355121396127318</v>
+        <v>0.6587605343935895</v>
       </c>
       <c r="T78">
-        <v>4.111734017345177</v>
+        <v>4.273832114447092</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.523683245427812</v>
+        <v>1.503895151331347</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2000249229105256</v>
+        <v>0.2375979082493561</v>
       </c>
       <c r="C79">
-        <v>2.682663209028616</v>
+        <v>1.250702404746482</v>
       </c>
       <c r="D79">
-        <v>6.951143209028615</v>
+        <v>5.589422404746482</v>
       </c>
       <c r="E79">
-        <v>4.45448</v>
+        <v>4.52472</v>
       </c>
       <c r="F79">
-        <v>5.40848</v>
+        <v>5.47872</v>
       </c>
       <c r="G79">
         <v>1.14</v>
@@ -7759,45 +7759,45 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M79">
-        <v>0.4867632</v>
+        <v>0.8042760960000001</v>
       </c>
       <c r="N79">
-        <v>0.2452776163265307</v>
+        <v>-0.07223527967346943</v>
       </c>
       <c r="O79">
-        <v>0.07358328489795919</v>
+        <v>-0.02167058390204083</v>
       </c>
       <c r="P79">
-        <v>0.1716943314285715</v>
+        <v>-0.05056469577142861</v>
       </c>
       <c r="Q79">
-        <v>0.2916943314285715</v>
+        <v>0.06943530422857139</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.6587605343935895</v>
+        <v>0.7016358565706129</v>
       </c>
       <c r="T79">
-        <v>4.273832114447092</v>
+        <v>4.572777835346908</v>
       </c>
       <c r="U79">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.3</v>
+        <v>0.273055790157363</v>
       </c>
       <c r="W79">
-        <v>0.063</v>
+        <v>0.1067154100048991</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y79">
-        <v>1.503895151331347</v>
+        <v>0.9101859671912101</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2375979082493561</v>
+        <v>0.2386079082493561</v>
       </c>
       <c r="C80">
-        <v>1.250702404746482</v>
+        <v>1.151182917820599</v>
       </c>
       <c r="D80">
-        <v>5.589422404746482</v>
+        <v>5.560142917820599</v>
       </c>
       <c r="E80">
-        <v>4.52472</v>
+        <v>4.59496</v>
       </c>
       <c r="F80">
-        <v>5.47872</v>
+        <v>5.54896</v>
       </c>
       <c r="G80">
         <v>1.14</v>
@@ -7841,37 +7841,37 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M80">
-        <v>0.8042760960000001</v>
+        <v>0.8145873280000001</v>
       </c>
       <c r="N80">
-        <v>-0.07223527967346943</v>
+        <v>-0.08254651167346949</v>
       </c>
       <c r="O80">
-        <v>-0.02167058390204083</v>
+        <v>-0.02476395350204085</v>
       </c>
       <c r="P80">
-        <v>-0.05056469577142861</v>
+        <v>-0.05778255817142865</v>
       </c>
       <c r="Q80">
-        <v>0.06943530422857139</v>
+        <v>0.06221744182857135</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.7016358565706129</v>
+        <v>0.7328661354549278</v>
       </c>
       <c r="T80">
-        <v>4.572777835346908</v>
+        <v>4.790529160839618</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.273055790157363</v>
+        <v>0.2695993877503078</v>
       </c>
       <c r="W80">
-        <v>0.1067154100048991</v>
+        <v>0.1072228098782548</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.9101859671912101</v>
+        <v>0.8986646258343594</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2386079082493561</v>
+        <v>0.2396179082493561</v>
       </c>
       <c r="C81">
-        <v>1.151182917820599</v>
+        <v>1.051968586203244</v>
       </c>
       <c r="D81">
-        <v>5.560142917820599</v>
+        <v>5.531168586203244</v>
       </c>
       <c r="E81">
-        <v>4.59496</v>
+        <v>4.6652</v>
       </c>
       <c r="F81">
-        <v>5.54896</v>
+        <v>5.6192</v>
       </c>
       <c r="G81">
         <v>1.14</v>
@@ -7923,37 +7923,37 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M81">
-        <v>0.8145873280000001</v>
+        <v>0.8248985600000001</v>
       </c>
       <c r="N81">
-        <v>-0.08254651167346949</v>
+        <v>-0.09285774367346944</v>
       </c>
       <c r="O81">
-        <v>-0.02476395350204085</v>
+        <v>-0.02785732310204083</v>
       </c>
       <c r="P81">
-        <v>-0.05778255817142865</v>
+        <v>-0.0650004205714286</v>
       </c>
       <c r="Q81">
-        <v>0.06221744182857135</v>
+        <v>0.05499957942857139</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.7328661354549278</v>
+        <v>0.7672194422276742</v>
       </c>
       <c r="T81">
-        <v>4.790529160839618</v>
+        <v>5.030055618881599</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2695993877503078</v>
+        <v>0.2662293954034289</v>
       </c>
       <c r="W81">
-        <v>0.1072228098782548</v>
+        <v>0.1077175247547766</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8986646258343594</v>
+        <v>0.8874313180114298</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2396179082493561</v>
+        <v>0.2406279082493561</v>
       </c>
       <c r="C82">
-        <v>1.051968586203244</v>
+        <v>0.9530546640620932</v>
       </c>
       <c r="D82">
-        <v>5.531168586203244</v>
+        <v>5.502494664062094</v>
       </c>
       <c r="E82">
-        <v>4.6652</v>
+        <v>4.735440000000001</v>
       </c>
       <c r="F82">
-        <v>5.6192</v>
+        <v>5.68944</v>
       </c>
       <c r="G82">
         <v>1.14</v>
@@ -8005,37 +8005,37 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M82">
-        <v>0.8248985600000001</v>
+        <v>0.8352097920000001</v>
       </c>
       <c r="N82">
-        <v>-0.09285774367346944</v>
+        <v>-0.1031689756734695</v>
       </c>
       <c r="O82">
-        <v>-0.02785732310204083</v>
+        <v>-0.03095069270204085</v>
       </c>
       <c r="P82">
-        <v>-0.0650004205714286</v>
+        <v>-0.07221828297142865</v>
       </c>
       <c r="Q82">
-        <v>0.05499957942857139</v>
+        <v>0.04778171702857134</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.7672194422276742</v>
+        <v>0.8051888865554467</v>
       </c>
       <c r="T82">
-        <v>5.030055618881599</v>
+        <v>5.294795388296421</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.2662293954034289</v>
+        <v>0.2629426127441273</v>
       </c>
       <c r="W82">
-        <v>0.1077175247547766</v>
+        <v>0.1082000244491621</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8874313180114298</v>
+        <v>0.8764753758137578</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2406279082493561</v>
+        <v>0.2416379082493561</v>
       </c>
       <c r="C83">
-        <v>0.9530546640620932</v>
+        <v>0.8544365034680457</v>
       </c>
       <c r="D83">
-        <v>5.502494664062094</v>
+        <v>5.474116503468046</v>
       </c>
       <c r="E83">
-        <v>4.735440000000001</v>
+        <v>4.805680000000001</v>
       </c>
       <c r="F83">
-        <v>5.68944</v>
+        <v>5.75968</v>
       </c>
       <c r="G83">
         <v>1.14</v>
@@ -8087,37 +8087,37 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M83">
-        <v>0.8352097920000001</v>
+        <v>0.8455210240000002</v>
       </c>
       <c r="N83">
-        <v>-0.1031689756734695</v>
+        <v>-0.1134802076734696</v>
       </c>
       <c r="O83">
-        <v>-0.03095069270204085</v>
+        <v>-0.03404406230204086</v>
       </c>
       <c r="P83">
-        <v>-0.07221828297142865</v>
+        <v>-0.07943614537142869</v>
       </c>
       <c r="Q83">
-        <v>0.04778171702857134</v>
+        <v>0.0405638546285713</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.8051888865554467</v>
+        <v>0.8473771580307492</v>
       </c>
       <c r="T83">
-        <v>5.294795388296421</v>
+        <v>5.588950687646222</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.2629426127441273</v>
+        <v>0.2597359955155404</v>
       </c>
       <c r="W83">
-        <v>0.1082000244491621</v>
+        <v>0.1086707558583187</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8764753758137578</v>
+        <v>0.865786651718468</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2416379082493561</v>
+        <v>0.2426479082493562</v>
       </c>
       <c r="C84">
-        <v>0.8544365034680457</v>
+        <v>0.7561095518835801</v>
       </c>
       <c r="D84">
-        <v>5.474116503468046</v>
+        <v>5.446029551883581</v>
       </c>
       <c r="E84">
-        <v>4.805680000000001</v>
+        <v>4.875920000000001</v>
       </c>
       <c r="F84">
-        <v>5.75968</v>
+        <v>5.82992</v>
       </c>
       <c r="G84">
         <v>1.14</v>
@@ -8169,37 +8169,37 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M84">
-        <v>0.8455210240000002</v>
+        <v>0.8558322560000001</v>
       </c>
       <c r="N84">
-        <v>-0.1134802076734696</v>
+        <v>-0.1237914396734695</v>
       </c>
       <c r="O84">
-        <v>-0.03404406230204086</v>
+        <v>-0.03713743190204085</v>
       </c>
       <c r="P84">
-        <v>-0.07943614537142869</v>
+        <v>-0.08665400777142865</v>
       </c>
       <c r="Q84">
-        <v>0.0405638546285713</v>
+        <v>0.03334599222857135</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.8473771580307492</v>
+        <v>0.89452875556197</v>
       </c>
       <c r="T84">
-        <v>5.588950687646222</v>
+        <v>5.917712492801884</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.2597359955155404</v>
+        <v>0.2566066461719797</v>
       </c>
       <c r="W84">
-        <v>0.1086707558583187</v>
+        <v>0.1091301443419534</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.865786651718468</v>
+        <v>0.8553554872399324</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2426479082493562</v>
+        <v>0.2436579082493562</v>
       </c>
       <c r="C85">
-        <v>0.7561095518835801</v>
+        <v>0.6580693497280494</v>
       </c>
       <c r="D85">
-        <v>5.446029551883581</v>
+        <v>5.41822934972805</v>
       </c>
       <c r="E85">
-        <v>4.875920000000001</v>
+        <v>4.946160000000001</v>
       </c>
       <c r="F85">
-        <v>5.82992</v>
+        <v>5.900160000000001</v>
       </c>
       <c r="G85">
         <v>1.14</v>
@@ -8251,37 +8251,37 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M85">
-        <v>0.8558322560000001</v>
+        <v>0.8661434880000002</v>
       </c>
       <c r="N85">
-        <v>-0.1237914396734695</v>
+        <v>-0.1341026716734696</v>
       </c>
       <c r="O85">
-        <v>-0.03713743190204085</v>
+        <v>-0.04023080150204087</v>
       </c>
       <c r="P85">
-        <v>-0.08665400777142865</v>
+        <v>-0.0938718701714287</v>
       </c>
       <c r="Q85">
-        <v>0.03334599222857135</v>
+        <v>0.02612812982857129</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.89452875556197</v>
+        <v>0.9475743027845933</v>
       </c>
       <c r="T85">
-        <v>5.917712492801884</v>
+        <v>6.287569523602003</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2566066461719797</v>
+        <v>0.2535518051461228</v>
       </c>
       <c r="W85">
-        <v>0.1091301443419534</v>
+        <v>0.1095785950045492</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8553554872399324</v>
+        <v>0.8451726838204092</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2436579082493562</v>
+        <v>0.2446679082493561</v>
       </c>
       <c r="C86">
-        <v>0.6580693497280503</v>
+        <v>0.5603115280171513</v>
       </c>
       <c r="D86">
-        <v>5.41822934972805</v>
+        <v>5.390711528017151</v>
       </c>
       <c r="E86">
-        <v>4.94616</v>
+        <v>5.0164</v>
       </c>
       <c r="F86">
-        <v>5.90016</v>
+        <v>5.9704</v>
       </c>
       <c r="G86">
         <v>1.14</v>
@@ -8333,37 +8333,37 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M86">
-        <v>0.8661434880000001</v>
+        <v>0.87645472</v>
       </c>
       <c r="N86">
-        <v>-0.1341026716734695</v>
+        <v>-0.1444139036734694</v>
       </c>
       <c r="O86">
-        <v>-0.04023080150204084</v>
+        <v>-0.04332417110204082</v>
       </c>
       <c r="P86">
-        <v>-0.09387187017142862</v>
+        <v>-0.1010897325714286</v>
       </c>
       <c r="Q86">
-        <v>0.02612812982857138</v>
+        <v>0.01891026742857141</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.9475743027845928</v>
+        <v>1.007692589636899</v>
       </c>
       <c r="T86">
-        <v>6.287569523601999</v>
+        <v>6.706740825175465</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2535518051461228</v>
+        <v>0.250568842732639</v>
       </c>
       <c r="W86">
-        <v>0.1095785950045492</v>
+        <v>0.1100164938868486</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8451726838204094</v>
+        <v>0.8352294757754635</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2446679082493561</v>
+        <v>0.2456779082493562</v>
       </c>
       <c r="C87">
-        <v>0.5603115280171513</v>
+        <v>0.4628318060739689</v>
       </c>
       <c r="D87">
-        <v>5.390711528017151</v>
+        <v>5.363471806073969</v>
       </c>
       <c r="E87">
-        <v>5.0164</v>
+        <v>5.08664</v>
       </c>
       <c r="F87">
-        <v>5.9704</v>
+        <v>6.04064</v>
       </c>
       <c r="G87">
         <v>1.14</v>
@@ -8415,37 +8415,37 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M87">
-        <v>0.87645472</v>
+        <v>0.8867659520000001</v>
       </c>
       <c r="N87">
-        <v>-0.1444139036734694</v>
+        <v>-0.1547251356734695</v>
       </c>
       <c r="O87">
-        <v>-0.04332417110204082</v>
+        <v>-0.04641754070204084</v>
       </c>
       <c r="P87">
-        <v>-0.1010897325714286</v>
+        <v>-0.1083075949714286</v>
       </c>
       <c r="Q87">
-        <v>0.01891026742857141</v>
+        <v>0.01169240502857137</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>1.007692589636899</v>
+        <v>1.076399203182392</v>
       </c>
       <c r="T87">
-        <v>6.706740825175465</v>
+        <v>7.185793741259426</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.250568842732639</v>
+        <v>0.2476552515380734</v>
       </c>
       <c r="W87">
-        <v>0.1100164938868486</v>
+        <v>0.1104442090742108</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8352294757754635</v>
+        <v>0.8255175051269115</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2456779082493562</v>
+        <v>0.2466879082493561</v>
       </c>
       <c r="C88">
-        <v>0.4628318060739689</v>
+        <v>0.365625989309077</v>
       </c>
       <c r="D88">
-        <v>5.363471806073969</v>
+        <v>5.336505989309077</v>
       </c>
       <c r="E88">
-        <v>5.08664</v>
+        <v>5.15688</v>
       </c>
       <c r="F88">
-        <v>6.04064</v>
+        <v>6.11088</v>
       </c>
       <c r="G88">
         <v>1.14</v>
@@ -8497,37 +8497,37 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M88">
-        <v>0.8867659520000001</v>
+        <v>0.897077184</v>
       </c>
       <c r="N88">
-        <v>-0.1547251356734695</v>
+        <v>-0.1650363676734694</v>
       </c>
       <c r="O88">
-        <v>-0.04641754070204084</v>
+        <v>-0.04951091030204082</v>
       </c>
       <c r="P88">
-        <v>-0.1083075949714286</v>
+        <v>-0.1155254573714286</v>
       </c>
       <c r="Q88">
-        <v>0.01169240502857137</v>
+        <v>0.004474542628571415</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>1.076399203182392</v>
+        <v>1.155676064965652</v>
       </c>
       <c r="T88">
-        <v>7.185793741259426</v>
+        <v>7.738547105971689</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2476552515380734</v>
+        <v>0.2448086394514289</v>
       </c>
       <c r="W88">
-        <v>0.1104442090742108</v>
+        <v>0.1108620917285302</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8255175051269115</v>
+        <v>0.8160287981714298</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2466879082493561</v>
+        <v>0.2476979082493562</v>
       </c>
       <c r="C89">
-        <v>0.365625989309077</v>
+        <v>0.268689967067254</v>
       </c>
       <c r="D89">
-        <v>5.336505989309077</v>
+        <v>5.309809967067254</v>
       </c>
       <c r="E89">
-        <v>5.15688</v>
+        <v>5.22712</v>
       </c>
       <c r="F89">
-        <v>6.11088</v>
+        <v>6.18112</v>
       </c>
       <c r="G89">
         <v>1.14</v>
@@ -8579,37 +8579,37 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M89">
-        <v>0.897077184</v>
+        <v>0.9073884160000001</v>
       </c>
       <c r="N89">
-        <v>-0.1650363676734694</v>
+        <v>-0.1753475996734695</v>
       </c>
       <c r="O89">
-        <v>-0.04951091030204082</v>
+        <v>-0.05260427990204084</v>
       </c>
       <c r="P89">
-        <v>-0.1155254573714286</v>
+        <v>-0.1227433197714286</v>
       </c>
       <c r="Q89">
-        <v>0.004474542628571415</v>
+        <v>-0.002743319771428637</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.155676064965652</v>
+        <v>1.248165737046124</v>
       </c>
       <c r="T89">
-        <v>7.738547105971689</v>
+        <v>8.383426031469332</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2448086394514289</v>
+        <v>0.2420267230940263</v>
       </c>
       <c r="W89">
-        <v>0.1108620917285302</v>
+        <v>0.111270477049797</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8160287981714298</v>
+        <v>0.8067557436467544</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2476979082493562</v>
+        <v>0.3072684100495617</v>
       </c>
       <c r="C90">
-        <v>0.268689967067254</v>
+        <v>-1.011287163861766</v>
       </c>
       <c r="D90">
-        <v>5.309809967067254</v>
+        <v>4.100072836138234</v>
       </c>
       <c r="E90">
-        <v>5.22712</v>
+        <v>5.29736</v>
       </c>
       <c r="F90">
-        <v>6.18112</v>
+        <v>6.25136</v>
       </c>
       <c r="G90">
         <v>1.14</v>
@@ -8661,45 +8661,45 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M90">
-        <v>0.9073884160000001</v>
+        <v>1.255273088</v>
       </c>
       <c r="N90">
-        <v>-0.1753475996734695</v>
+        <v>-0.5232322716734694</v>
       </c>
       <c r="O90">
-        <v>-0.05260427990204084</v>
+        <v>-0.1569696815020408</v>
       </c>
       <c r="P90">
-        <v>-0.1227433197714286</v>
+        <v>-0.3662625901714286</v>
       </c>
       <c r="Q90">
-        <v>-0.002743319771428637</v>
+        <v>-0.2462625901714286</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.248165737046124</v>
+        <v>1.452930820415822</v>
       </c>
       <c r="T90">
-        <v>8.383426031469332</v>
+        <v>9.811138812502833</v>
       </c>
       <c r="U90">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.2420267230940263</v>
+        <v>0.1749517670675651</v>
       </c>
       <c r="W90">
-        <v>0.111270477049797</v>
+        <v>0.1656696851728329</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y90">
-        <v>0.8067557436467544</v>
+        <v>0.5831725568918837</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3072684100495617</v>
+        <v>0.3088184100495617</v>
       </c>
       <c r="C91">
-        <v>-1.011287163861766</v>
+        <v>-1.105689399861963</v>
       </c>
       <c r="D91">
-        <v>4.100072836138234</v>
+        <v>4.075910600138037</v>
       </c>
       <c r="E91">
-        <v>5.29736</v>
+        <v>5.3676</v>
       </c>
       <c r="F91">
-        <v>6.25136</v>
+        <v>6.3216</v>
       </c>
       <c r="G91">
         <v>1.14</v>
@@ -8743,37 +8743,37 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M91">
-        <v>1.255273088</v>
+        <v>1.26937728</v>
       </c>
       <c r="N91">
-        <v>-0.5232322716734694</v>
+        <v>-0.5373364636734694</v>
       </c>
       <c r="O91">
-        <v>-0.1569696815020408</v>
+        <v>-0.1612009391020408</v>
       </c>
       <c r="P91">
-        <v>-0.3662625901714286</v>
+        <v>-0.3761355245714286</v>
       </c>
       <c r="Q91">
-        <v>-0.2462625901714286</v>
+        <v>-0.2561355245714286</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.452930820415822</v>
+        <v>1.593643902457404</v>
       </c>
       <c r="T91">
-        <v>9.811138812502833</v>
+        <v>10.79225269375311</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1749517670675651</v>
+        <v>0.1730078585445922</v>
       </c>
       <c r="W91">
-        <v>0.1656696851728329</v>
+        <v>0.1660600220042459</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5831725568918837</v>
+        <v>0.5766928618153073</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3088184100495617</v>
+        <v>0.3103684100495617</v>
       </c>
       <c r="C92">
-        <v>-1.105689399861963</v>
+        <v>-1.199808522199474</v>
       </c>
       <c r="D92">
-        <v>4.075910600138037</v>
+        <v>4.052031477800527</v>
       </c>
       <c r="E92">
-        <v>5.3676</v>
+        <v>5.43784</v>
       </c>
       <c r="F92">
-        <v>6.3216</v>
+        <v>6.39184</v>
       </c>
       <c r="G92">
         <v>1.14</v>
@@ -8825,37 +8825,37 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M92">
-        <v>1.26937728</v>
+        <v>1.283481472</v>
       </c>
       <c r="N92">
-        <v>-0.5373364636734694</v>
+        <v>-0.5514406556734694</v>
       </c>
       <c r="O92">
-        <v>-0.1612009391020408</v>
+        <v>-0.1654321967020408</v>
       </c>
       <c r="P92">
-        <v>-0.3761355245714286</v>
+        <v>-0.3860084589714287</v>
       </c>
       <c r="Q92">
-        <v>-0.2561355245714286</v>
+        <v>-0.2660084589714287</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.593643902457404</v>
+        <v>1.765626558286005</v>
       </c>
       <c r="T92">
-        <v>10.79225269375311</v>
+        <v>11.99139188194791</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1730078585445922</v>
+        <v>0.1711066732858604</v>
       </c>
       <c r="W92">
-        <v>0.1660600220042459</v>
+        <v>0.1664417800041992</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5766928618153073</v>
+        <v>0.5703555776195346</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3103684100495617</v>
+        <v>0.3119184100495617</v>
       </c>
       <c r="C93">
-        <v>-1.199808522199474</v>
+        <v>-1.293649477839563</v>
       </c>
       <c r="D93">
-        <v>4.052031477800527</v>
+        <v>4.028430522160438</v>
       </c>
       <c r="E93">
-        <v>5.43784</v>
+        <v>5.508080000000001</v>
       </c>
       <c r="F93">
-        <v>6.39184</v>
+        <v>6.46208</v>
       </c>
       <c r="G93">
         <v>1.14</v>
@@ -8907,37 +8907,37 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M93">
-        <v>1.283481472</v>
+        <v>1.297585664</v>
       </c>
       <c r="N93">
-        <v>-0.5514406556734694</v>
+        <v>-0.5655448476734695</v>
       </c>
       <c r="O93">
-        <v>-0.1654321967020408</v>
+        <v>-0.1696634543020408</v>
       </c>
       <c r="P93">
-        <v>-0.3860084589714287</v>
+        <v>-0.3958813933714286</v>
       </c>
       <c r="Q93">
-        <v>-0.2660084589714287</v>
+        <v>-0.2758813933714286</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.765626558286005</v>
+        <v>1.980604878071756</v>
       </c>
       <c r="T93">
-        <v>11.99139188194791</v>
+        <v>13.4903158671914</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1711066732858604</v>
+        <v>0.1692468181414489</v>
       </c>
       <c r="W93">
-        <v>0.1664417800041992</v>
+        <v>0.1668152389171971</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5703555776195346</v>
+        <v>0.5641560604714961</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3119184100495617</v>
+        <v>0.3134684100495617</v>
       </c>
       <c r="C94">
-        <v>-1.293649477839563</v>
+        <v>-1.387217099161005</v>
       </c>
       <c r="D94">
-        <v>4.028430522160438</v>
+        <v>4.005102900838995</v>
       </c>
       <c r="E94">
-        <v>5.508080000000001</v>
+        <v>5.578320000000001</v>
       </c>
       <c r="F94">
-        <v>6.46208</v>
+        <v>6.53232</v>
       </c>
       <c r="G94">
         <v>1.14</v>
@@ -8989,37 +8989,37 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M94">
-        <v>1.297585664</v>
+        <v>1.311689856</v>
       </c>
       <c r="N94">
-        <v>-0.5655448476734695</v>
+        <v>-0.5796490396734695</v>
       </c>
       <c r="O94">
-        <v>-0.1696634543020408</v>
+        <v>-0.1738947119020408</v>
       </c>
       <c r="P94">
-        <v>-0.3958813933714286</v>
+        <v>-0.4057543277714286</v>
       </c>
       <c r="Q94">
-        <v>-0.2758813933714286</v>
+        <v>-0.2857543277714286</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.980604878071756</v>
+        <v>2.25700557493915</v>
       </c>
       <c r="T94">
-        <v>13.4903158671914</v>
+        <v>15.41750384821874</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1692468181414489</v>
+        <v>0.1674269598818634</v>
       </c>
       <c r="W94">
-        <v>0.1668152389171971</v>
+        <v>0.1671806664557218</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5641560604714961</v>
+        <v>0.5580898662728779</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3134684100495617</v>
+        <v>0.3150184100495617</v>
       </c>
       <c r="C95">
-        <v>-1.387217099161005</v>
+        <v>-1.480516107254685</v>
       </c>
       <c r="D95">
-        <v>4.005102900838995</v>
+        <v>3.982043892745315</v>
       </c>
       <c r="E95">
-        <v>5.578320000000001</v>
+        <v>5.648560000000001</v>
       </c>
       <c r="F95">
-        <v>6.53232</v>
+        <v>6.60256</v>
       </c>
       <c r="G95">
         <v>1.14</v>
@@ -9071,37 +9071,37 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M95">
-        <v>1.311689856</v>
+        <v>1.325794048</v>
       </c>
       <c r="N95">
-        <v>-0.5796490396734695</v>
+        <v>-0.5937532316734695</v>
       </c>
       <c r="O95">
-        <v>-0.1738947119020408</v>
+        <v>-0.1781259695020408</v>
       </c>
       <c r="P95">
-        <v>-0.4057543277714286</v>
+        <v>-0.4156272621714286</v>
       </c>
       <c r="Q95">
-        <v>-0.2857543277714286</v>
+        <v>-0.2956272621714287</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>2.25700557493915</v>
+        <v>2.625539837429009</v>
       </c>
       <c r="T95">
-        <v>15.41750384821874</v>
+        <v>17.98708782292188</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1674269598818634</v>
+        <v>0.1656458220107797</v>
       </c>
       <c r="W95">
-        <v>0.1671806664557218</v>
+        <v>0.1675383189402354</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5580898662728779</v>
+        <v>0.5521527400359325</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3150184100495617</v>
+        <v>0.3165684100495617</v>
       </c>
       <c r="C96">
-        <v>-1.480516107254685</v>
+        <v>-1.573551115108908</v>
       </c>
       <c r="D96">
-        <v>3.982043892745315</v>
+        <v>3.959248884891093</v>
       </c>
       <c r="E96">
-        <v>5.648560000000001</v>
+        <v>5.718800000000001</v>
       </c>
       <c r="F96">
-        <v>6.60256</v>
+        <v>6.672800000000001</v>
       </c>
       <c r="G96">
         <v>1.14</v>
@@ -9153,37 +9153,37 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M96">
-        <v>1.325794048</v>
+        <v>1.33989824</v>
       </c>
       <c r="N96">
-        <v>-0.5937532316734695</v>
+        <v>-0.6078574236734695</v>
       </c>
       <c r="O96">
-        <v>-0.1781259695020408</v>
+        <v>-0.1823572271020409</v>
       </c>
       <c r="P96">
-        <v>-0.4156272621714286</v>
+        <v>-0.4255001965714287</v>
       </c>
       <c r="Q96">
-        <v>-0.2956272621714287</v>
+        <v>-0.3055001965714287</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.625539837429009</v>
+        <v>3.141487804914812</v>
       </c>
       <c r="T96">
-        <v>17.98708782292188</v>
+        <v>21.58450538750626</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1656458220107797</v>
+        <v>0.1639021817790873</v>
       </c>
       <c r="W96">
-        <v>0.1675383189402354</v>
+        <v>0.1678884418987593</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5521527400359325</v>
+        <v>0.5463406059302911</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3165684100495617</v>
+        <v>0.3181184100495618</v>
       </c>
       <c r="C97">
-        <v>-1.573551115108908</v>
+        <v>-1.666326630685929</v>
       </c>
       <c r="D97">
-        <v>3.959248884891093</v>
+        <v>3.936713369314072</v>
       </c>
       <c r="E97">
-        <v>5.718800000000001</v>
+        <v>5.789040000000001</v>
       </c>
       <c r="F97">
-        <v>6.672800000000001</v>
+        <v>6.743040000000001</v>
       </c>
       <c r="G97">
         <v>1.14</v>
@@ -9235,37 +9235,37 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M97">
-        <v>1.33989824</v>
+        <v>1.354002432</v>
       </c>
       <c r="N97">
-        <v>-0.6078574236734695</v>
+        <v>-0.6219616156734695</v>
       </c>
       <c r="O97">
-        <v>-0.1823572271020409</v>
+        <v>-0.1865884847020408</v>
       </c>
       <c r="P97">
-        <v>-0.4255001965714287</v>
+        <v>-0.4353731309714287</v>
       </c>
       <c r="Q97">
-        <v>-0.3055001965714287</v>
+        <v>-0.3153731309714287</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>3.141487804914812</v>
+        <v>3.915409756143517</v>
       </c>
       <c r="T97">
-        <v>21.58450538750626</v>
+        <v>26.98063173438284</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1639021817790873</v>
+        <v>0.1621948673855552</v>
       </c>
       <c r="W97">
-        <v>0.1678884418987593</v>
+        <v>0.1682312706289806</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5463406059302911</v>
+        <v>0.5406495579518505</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3181184100495617</v>
+        <v>0.3196684100495618</v>
       </c>
       <c r="C98">
-        <v>-1.666326630685926</v>
+        <v>-1.758847059894001</v>
       </c>
       <c r="D98">
-        <v>3.936713369314073</v>
+        <v>3.914432940105999</v>
       </c>
       <c r="E98">
-        <v>5.78904</v>
+        <v>5.85928</v>
       </c>
       <c r="F98">
-        <v>6.74304</v>
+        <v>6.81328</v>
       </c>
       <c r="G98">
         <v>1.14</v>
@@ -9317,37 +9317,37 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M98">
-        <v>1.354002432</v>
+        <v>1.368106624</v>
       </c>
       <c r="N98">
-        <v>-0.6219616156734693</v>
+        <v>-0.6360658076734693</v>
       </c>
       <c r="O98">
-        <v>-0.1865884847020408</v>
+        <v>-0.1908197423020408</v>
       </c>
       <c r="P98">
-        <v>-0.4353731309714285</v>
+        <v>-0.4452460653714285</v>
       </c>
       <c r="Q98">
-        <v>-0.3153731309714285</v>
+        <v>-0.3252460653714285</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>3.915409756143507</v>
+        <v>5.20527967485801</v>
       </c>
       <c r="T98">
-        <v>26.98063173438277</v>
+        <v>35.97417564584369</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1621948673855552</v>
+        <v>0.1605227553506526</v>
       </c>
       <c r="W98">
-        <v>0.1682312706289805</v>
+        <v>0.168567030725589</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5406495579518507</v>
+        <v>0.5350758511688418</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3196684100495618</v>
+        <v>0.3212184100495618</v>
       </c>
       <c r="C99">
-        <v>-1.758847059894001</v>
+        <v>-1.851116709459085</v>
       </c>
       <c r="D99">
-        <v>3.914432940105999</v>
+        <v>3.892403290540915</v>
       </c>
       <c r="E99">
-        <v>5.85928</v>
+        <v>5.92952</v>
       </c>
       <c r="F99">
-        <v>6.81328</v>
+        <v>6.88352</v>
       </c>
       <c r="G99">
         <v>1.14</v>
@@ -9399,37 +9399,37 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M99">
-        <v>1.368106624</v>
+        <v>1.382210816</v>
       </c>
       <c r="N99">
-        <v>-0.6360658076734693</v>
+        <v>-0.6501699996734693</v>
       </c>
       <c r="O99">
-        <v>-0.1908197423020408</v>
+        <v>-0.1950509999020408</v>
       </c>
       <c r="P99">
-        <v>-0.4452460653714285</v>
+        <v>-0.4551189997714286</v>
       </c>
       <c r="Q99">
-        <v>-0.3252460653714285</v>
+        <v>-0.3351189997714286</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>5.20527967485801</v>
+        <v>7.785019512287014</v>
       </c>
       <c r="T99">
-        <v>35.97417564584369</v>
+        <v>53.96126346876553</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1605227553506526</v>
+        <v>0.1588847680511561</v>
       </c>
       <c r="W99">
-        <v>0.168567030725589</v>
+        <v>0.1688959385753279</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5350758511688418</v>
+        <v>0.5296158935038536</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3212184100495618</v>
+        <v>0.3227684100495617</v>
       </c>
       <c r="C100">
-        <v>-1.851116709459085</v>
+        <v>-1.943139789700107</v>
       </c>
       <c r="D100">
-        <v>3.892403290540915</v>
+        <v>3.870620210299892</v>
       </c>
       <c r="E100">
-        <v>5.92952</v>
+        <v>5.99976</v>
       </c>
       <c r="F100">
-        <v>6.88352</v>
+        <v>6.95376</v>
       </c>
       <c r="G100">
         <v>1.14</v>
@@ -9481,37 +9481,37 @@
         <v>0.7320408163265306</v>
       </c>
       <c r="M100">
-        <v>1.382210816</v>
+        <v>1.396315008</v>
       </c>
       <c r="N100">
-        <v>-0.6501699996734693</v>
+        <v>-0.6642741916734693</v>
       </c>
       <c r="O100">
-        <v>-0.1950509999020408</v>
+        <v>-0.1992822575020408</v>
       </c>
       <c r="P100">
-        <v>-0.4551189997714286</v>
+        <v>-0.4649919341714286</v>
       </c>
       <c r="Q100">
-        <v>-0.3351189997714286</v>
+        <v>-0.3449919341714286</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>7.785019512287014</v>
+        <v>15.52423902457403</v>
       </c>
       <c r="T100">
-        <v>53.96126346876553</v>
+        <v>107.9225269375311</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1588847680511561</v>
+        <v>0.1572798714041747</v>
       </c>
       <c r="W100">
-        <v>0.1688959385753279</v>
+        <v>0.1692182018220417</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5296158935038536</v>
+        <v>0.5242662380139157</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3227684100495617</v>
-      </c>
-      <c r="C101">
-        <v>-1.943139789700107</v>
-      </c>
-      <c r="D101">
-        <v>3.870620210299892</v>
-      </c>
-      <c r="E101">
-        <v>5.99976</v>
-      </c>
-      <c r="F101">
-        <v>6.95376</v>
-      </c>
-      <c r="G101">
-        <v>1.14</v>
-      </c>
-      <c r="H101">
-        <v>6.07</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.8520408163265306</v>
-      </c>
-      <c r="K101">
-        <v>0.12</v>
-      </c>
-      <c r="L101">
-        <v>0.7320408163265306</v>
-      </c>
-      <c r="M101">
-        <v>1.396315008</v>
-      </c>
-      <c r="N101">
-        <v>-0.6642741916734693</v>
-      </c>
-      <c r="O101">
-        <v>-0.1992822575020408</v>
-      </c>
-      <c r="P101">
-        <v>-0.4649919341714286</v>
-      </c>
-      <c r="Q101">
-        <v>-0.3449919341714286</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>15.52423902457403</v>
-      </c>
-      <c r="T101">
-        <v>107.9225269375311</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1572798714041747</v>
-      </c>
-      <c r="W101">
-        <v>0.1692182018220417</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5242662380139157</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
